--- a/NSP Catalogue of Resources.xlsx
+++ b/NSP Catalogue of Resources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifrcorg-my.sharepoint.com/personal/belen_zazu_ifrc_org1/Documents/Escritorio/NSP Catalogue of Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3773" documentId="13_ncr:1_{A22110D1-A295-4D58-AA0C-0F9F0C343F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DBFCD66-9F10-43B5-9E3A-F75B950ACCCA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A04FF6CC-6691-4217-A9F2-B0CD1089E23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{B3C95166-E850-41AC-8E34-8926B04F3AE7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="3" xr2:uid="{B3C95166-E850-41AC-8E34-8926B04F3AE7}"/>
   </bookViews>
   <sheets>
     <sheet name="PER Catalogue of Resources" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,6 @@
     <definedName name="Filepath">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -198,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3589" uniqueCount="1680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3630" uniqueCount="1722">
   <si>
     <t>PER Catalogue of Resources</t>
   </si>
@@ -4524,19 +4523,85 @@
     <t>Under revision</t>
   </si>
   <si>
+    <t>Titles</t>
+  </si>
+  <si>
+    <t>Pop-up titles</t>
+  </si>
+  <si>
+    <t>English link</t>
+  </si>
+  <si>
+    <t>Spanish link</t>
+  </si>
+  <si>
+    <t>French link</t>
+  </si>
+  <si>
+    <t>Arabic link</t>
+  </si>
+  <si>
+    <t>PER Full Capacity Enhancement</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/Ej7GrnSMHR5BiIfjdeCg4gcBS9Ab1GZEVEm8YAmR-Vim8Q?e=lwXsGZ</t>
+  </si>
+  <si>
+    <t>Self-Assessment</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCBxmP9IC_qRKWXEpeowT56AfUH8l-Z2g06NIsUVzGhGkI</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBvGDPLiOAwSLY9vIsV9qS5ATahW_BWIKX80foqunfKhcE?e=pGJsyr</t>
+  </si>
+  <si>
+    <t>Simulation</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCUBNyOp8nVQLqxWkXPjBD_AT3TEIz1q8AQ6weOai8jHk8</t>
+  </si>
+  <si>
+    <t>Supported data collection</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgA1UxgEQb_zR4PzVv_M6vymATebJNIHeV_RbxtJI7tnzDQ</t>
+  </si>
+  <si>
     <t>Operational</t>
   </si>
   <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCkkq62OBEeTLppbfGGr_NxAeEofD10cJDWaawdvkrbLZY</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgA71FDZ1-WCR4ZENtLWTjmPAeNmU5pkMFF28TQvf3qmc2s?e=20EVAw</t>
+  </si>
+  <si>
     <t>Post-operational</t>
   </si>
   <si>
-    <t>Self-Assessment</t>
-  </si>
-  <si>
-    <t>Simulation</t>
-  </si>
-  <si>
-    <t>Supported data collection</t>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDCYsSO1vzUSp7UdIyOTjiCAcM3RoNkoek0Gc06-xhDLzA</t>
+  </si>
+  <si>
+    <t>Preparedness and Response Capacity enhancement in Branches</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgAAEmMZ0FfNQau7cPIg6eHOAcaOEGfM1MP9h7KL2V-NcYU</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBmIwcAH-5zTKFD-krsnZuYARc2YFX8d0kMvpq1qFvMnEw</t>
+  </si>
+  <si>
+    <t>Readiness Check</t>
+  </si>
+  <si>
+    <t>Rapid Response Check</t>
+  </si>
+  <si>
+    <t>Learnings from Operations</t>
+  </si>
+  <si>
+    <t>PROGRAMMES AND SERVICES, SECTORS AND CROSS-CUTTING AREAS</t>
   </si>
   <si>
     <t>Migration and Displacement</t>
@@ -4554,76 +4619,7 @@
     <t>Livelihoods</t>
   </si>
   <si>
-    <t>English link</t>
-  </si>
-  <si>
-    <t>French link</t>
-  </si>
-  <si>
-    <t>Spanish link</t>
-  </si>
-  <si>
-    <t>Arabic link</t>
-  </si>
-  <si>
-    <t>PER Full Capacity Enhancement</t>
-  </si>
-  <si>
-    <t>Pop-up titles</t>
-  </si>
-  <si>
-    <t>Titles</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/Ej7GrnSMHR5BiIfjdeCg4gcBS9Ab1GZEVEm8YAmR-Vim8Q?e=lwXsGZ</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCBxmP9IC_qRKWXEpeowT56AfUH8l-Z2g06NIsUVzGhGkI</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBvGDPLiOAwSLY9vIsV9qS5ATahW_BWIKX80foqunfKhcE?e=pGJsyr</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgA71FDZ1-WCR4ZENtLWTjmPAeNmU5pkMFF28TQvf3qmc2s?e=20EVAw</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCkkq62OBEeTLppbfGGr_NxAeEofD10cJDWaawdvkrbLZY</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDCYsSO1vzUSp7UdIyOTjiCAcM3RoNkoek0Gc06-xhDLzA</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgA1UxgEQb_zR4PzVv_M6vymATebJNIHeV_RbxtJI7tnzDQ</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCUBNyOp8nVQLqxWkXPjBD_AT3TEIz1q8AQ6weOai8jHk8</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgAAEmMZ0FfNQau7cPIg6eHOAcaOEGfM1MP9h7KL2V-NcYU</t>
-  </si>
-  <si>
-    <t>Preparedness and Response Capacity enhancement in Branches</t>
-  </si>
-  <si>
-    <t>Readiness Check</t>
-  </si>
-  <si>
-    <t>Rapid Response Check</t>
-  </si>
-  <si>
-    <t>Learnings from Operations</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBmIwcAH-5zTKFD-krsnZuYARc2YFX8d0kMvpq1qFvMnEw</t>
-  </si>
-  <si>
-    <t>PROGRAMMES AND SERVICES, SECTORS AND CROSS-CUTTING AREAS</t>
-  </si>
-  <si>
-    <t>National Society Preparedness - Introduction</t>
-  </si>
-  <si>
-    <t>Technological and Biological Hazards</t>
+    <t>Section</t>
   </si>
   <si>
     <t>Type of Resource</t>
@@ -4632,6 +4628,9 @@
     <t>Resources</t>
   </si>
   <si>
+    <t>Popup</t>
+  </si>
+  <si>
     <t>Region</t>
   </si>
   <si>
@@ -4654,6 +4653,21 @@
   </si>
   <si>
     <t>Link Portuguese</t>
+  </si>
+  <si>
+    <t>NSP Reference Materials</t>
+  </si>
+  <si>
+    <t>Core document</t>
+  </si>
+  <si>
+    <t>NS Preparedness Framework</t>
+  </si>
+  <si>
+    <t>https://www.ifrc.org/sites/default/files/2025-09/Marco%20para%20la%20preparaci%C3%B3n%20de%20las%20Sociedades%20Nacionales%20de%20IFRC.pdf</t>
+  </si>
+  <si>
+    <t>The PER Approach</t>
   </si>
   <si>
     <t xml:space="preserve">https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/EgZ-8br2x6tPu1Zx53mOhPABdTYFroJQDAUpJY_QICfw2g
@@ -4666,6 +4680,24 @@
     <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/EokyN45Ul9VOjLTgLkVfvO0BhlBphGRk6m89bFvUcTJrAQ</t>
   </si>
   <si>
+    <t>The PER Mechanism</t>
+  </si>
+  <si>
+    <t>NS Preparedness leaflet</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:b:/s/IFRCSharing/EXKvUpUXf09KrMRsJbjDMBYBgeq1VxRRYj-8h1ti1qP4lg</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:b:/s/IFRCSharing/EeIRNHF_ZfdHoXBjSyrXjYIBWLdOIunH4vlhj9zRxTdkig</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:b:/s/IFRCSharing/EbjrNJnBu1tAsdaDGU0Gn0MB1bdCRAeTb4nvdLJJLJIRnw?e=qTADTC</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:b:/s/IFRCSharing/EfxfkvNw8PBMkOVo_lTZXDwBY9VMjC5CLKqAkj8uUjJsYA?e=cUY1dT</t>
+  </si>
+  <si>
     <t>PER Mechanism detailed - collapsible document</t>
   </si>
   <si>
@@ -4756,6 +4788,12 @@
     <t>Course</t>
   </si>
   <si>
+    <t>PER Learning course</t>
+  </si>
+  <si>
+    <t>PER Learning videos</t>
+  </si>
+  <si>
     <t>Video</t>
   </si>
   <si>
@@ -4810,9 +4848,210 @@
     <t>PER TWG Members (Updated June 2023)</t>
   </si>
   <si>
+    <t>PER in the DRM Continuum</t>
+  </si>
+  <si>
+    <t>Tools</t>
+  </si>
+  <si>
+    <t>NSD-NSP</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCQuAdRTIMbToMpPI3hCw9dAcCbpFKHu0p_B9KQFTYa6ZQ</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCM0JFInL5jRodrE8pCUJemASyMKpYPSgPUrLY1fGwT8jU?e=1iVyEd</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCaxu03v6WYQKv2Uv4wxvyNAe3yCICk_ujlpfokjrW3bv8</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDibu6TrZzBS67wHfhJMSGpAZc2R_7l_-GvGIkhOSzri90</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgArZ1xGlQmsSpKJn8Woep-JAcjK8_vXzlJPRoX8QZ4YQBI</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBku3KFPY4ERaUtUCRylnxjAXFIC9d9gSDuQEM0hG_A0Mk</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBvGDPLiOAwSLY9vIsV9qS5ATahW_BWIKX80foqunfKhcE</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBRbjxlYE3_T5y3J6m9CC1HATPOdZRH-DDRFgPJYwI4b94</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCCdFJWj2bkTYBSAxpGZsyJAVPvkddv1aFaHdBHw6wE0f0</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgAsSCE0kA7GSbpl_stBPfSkAd9cNAw_M2HyeKXaCXyEKdA</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgAEdhnHYyvxRrEpi9NFct9ZAW34m0FXgbMdro4hz336BGw</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgA71FDZ1-WCR4ZENtLWTjmPAeNmU5pkMFF28TQvf3qmc2s</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBvu9oyoYANRJ1AUAUFZxC9Ac62GVDJ5T-v8fB7iipm3fo?e=KBH0Zj</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgAdUJ8R5HyqRonRP-It1HcCAad9_rZ59gEnLNc6nJU6Cps</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBPxcHRNBmGQ4OrLUmZcqrkAW3XpgFrERG_E0t2ETuDJSM</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDvtGvGtLVYQJkARvMz4p_CARIrNYYMQXxHJ1osLIcavaE?e=b4jPYq</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDjfPBIDgnkTqo9InYcTUZZAZPaS64bPhxpYGkcbaqiEHA</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDkmWE42EyqTaLq4DZSb0NoAXDXnpqVixJqhhpOLXmqgn8</t>
+  </si>
+  <si>
     <t>Readiness check</t>
   </si>
   <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgALVB8KXrLtSIzZ893caSBvATXkabA_iaFjdVVqjVVOFgI</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDpalvDnsaARqbd526E9LKmAbpaxUeNMWNQpeW4u7K7lrQ</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDCZGVz_UkXQaCTuqG9xUP9AbqHnz2Vd8zHgdonLW037DY</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCCWonGqwrZQ4aap_x21Ze2AaHm3daD6odVzFZDK9MpTMU</t>
+  </si>
+  <si>
+    <t>Rapid Response check</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDwwnR3rmlsQ5b0RrGc3io8AXcHltgyPpuYbrnIQdR16-I</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDhX1PgM2NqQKyHRzwqAFjCAbiX0X3JZ58nA29LgiYwX_I</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBRn4ahXIqRQ5MIeBVtlcFSAbNffPorERwzax69yGja0y8</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBvT8L3oRsDRZ7Hm_jTnJ47AV9zp2kvSa3f2DNUeELVIQQ</t>
+  </si>
+  <si>
+    <t>Learnings from operations</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBk1neqyK2uT7WmsyrWNp1ZAVxR5yhej2LOTY9nSz7lBDY</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCkTR9OrXr8T6QxYJEPXffqAfiiSdDC1_KCZLmxXsb4wBE</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCv-LQd0sq7T6SWOKlrwi7MAf6xDAs2NdqaBCkD0dp22LA</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgD9x60KmJ15RoJ8fVeRP-7HAYn75O9rqn0YP5859V9Qn2M</t>
+  </si>
+  <si>
+    <t>Linkages</t>
+  </si>
+  <si>
+    <t>NS Preparedness links to key topics</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBv7aZfU-IUQY9sAHIHlWJGAQmLAQgb_cGtGzR9AINCCwM</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDJBqa4OZoZQ6F5fd-UlIjxAd-5hR7Out3cmzhkaP4kL6I</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgAgjEEWNIW-TL8V_zckMDQVAZmKbY6LQRkPrpyoWjVj1ac</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgC1tfQ5gMnLQ7QLFoDC0ac3AUsE9TA4YkVp1nYBwW8KWII</t>
+  </si>
+  <si>
+    <t>NS Preparedness links to Migration and Displacement</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgB0-1YOM9aETIkHK1COoxvXAUKY7oK-YXIbzCFWedMsB-I</t>
+  </si>
+  <si>
+    <t>Climate and environment</t>
+  </si>
+  <si>
+    <t>NS Preparedness links to Environmental and Climate</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDvAlO3V1eQRbwBd6N9WFz3AY-xyajRbz_GrSrxr6uxrmU</t>
+  </si>
+  <si>
+    <t>NS Preparedness links to PGI</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgASGMib140hQrhZQSdGSH9_AZzdh44KT20zkkWAfh_qmFQ</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCX3SlZQO1WSY-7f2ZFVx2TAXoPYm6mtY7T6K5If3wtwLU</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCU_NuQ6a6vQrHz3cIcGp3EATnBu-UgAFPPP-j4gQcQdZk</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgARAI0UeLTqRJnS_09mHJzBAbmYqImr_CWxK6gucUnqWYU</t>
+  </si>
+  <si>
+    <t>NS Preparedness links to CEA</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgC0WXwnsUPRTLXWhNT8ATWpAS9ZYUacbW3o1pJsiRyPorg</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDyAmf6lmfjTIL6wz6y2DmWAYrlTii_iN1tvuAaNjBeyek</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBdXH_K96qjQLtHfp8W9bwnAUF5eT_GmnN7q3ci_487Em8</t>
+  </si>
+  <si>
+    <t>NS Preparedness links to Health</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgB9EmeRgkHIR4xM-qYzby_3AVBirR01ho2SMgnUBD_Hyrc</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgAl9BRTMx3fR5sFjv_UHl9HAahDNyTtgn82u6uLFQMKMvQ</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCK7s-YPZoSTqbekWp203OBAa0G5wG9ZA1zO8A0b7nOSYY?e=grq1ps</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgB197K6nNpuTKZ3132Apc_CAQuakH5tXsFp9EOrI4r4RAY?e=6C9CDQ</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgB3dTRw7qyeQJCGTmD9TBGZAUjrLl70h_C4jCMHNz4MrKA</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgA3gX_yGfOBQYpVjDeedRVqAXeZm3l2Ij85PN6ZgnaC4eE</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDsTGXTseZsQp4rBFgYf8oiAb-efSSoQkNMXJPrwjSxKvk?e=oJgafB</t>
+  </si>
+  <si>
+    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgAI3hVkHFfiT4ZXRGceKEElAY2LGeskoIXnbrcJYK-lk60?e=Bg7KIN</t>
+  </si>
+  <si>
+    <t>NSP Channels</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>IFRC Webpage</t>
+  </si>
+  <si>
     <t>Disaster preparedness webpage</t>
   </si>
   <si>
@@ -4822,30 +5061,48 @@
     <t>LinkedIn Group</t>
   </si>
   <si>
+    <t>to showcase experiences</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/groups/12885483/</t>
   </si>
   <si>
     <t>Youtube playlist</t>
   </si>
   <si>
+    <t>NS Preparedness playlist</t>
+  </si>
+  <si>
     <t>https://youtube.com/playlist?list=PLf2g_NkFyyv6FYkh5QX_ao50BREcAw35q&amp;si=NNeIWKcMIeGfwndB</t>
   </si>
   <si>
     <t>Newsletter</t>
   </si>
   <si>
+    <t>Quarterly published</t>
+  </si>
+  <si>
     <t>https://us1.campaign-archive.com/home/?u=695a3c121858dc1c6820969c0&amp;id=c66ee979f7</t>
   </si>
   <si>
+    <t>Community of Practice</t>
+  </si>
+  <si>
+    <t>NS Preparedness CoP</t>
+  </si>
+  <si>
+    <t>https://ifrc.us1.list-manage.com/track/click?u=695a3c121858dc1c6820969c0&amp;id=bb7a64c1da&amp;e=00e7561d24</t>
+  </si>
+  <si>
+    <t>Success stories</t>
+  </si>
+  <si>
     <t>NS Preparedness: COVID-19 sucess stories</t>
   </si>
   <si>
     <t>Global</t>
   </si>
   <si>
-    <t>NS Preparedness leaflet</t>
-  </si>
-  <si>
     <t>Case study</t>
   </si>
   <si>
@@ -4879,6 +5136,9 @@
     <t>Article</t>
   </si>
   <si>
+    <t>A more effective response is possible: Panama</t>
+  </si>
+  <si>
     <t>https://www.ifrc.org/article/more-effective-response-possible</t>
   </si>
   <si>
@@ -4966,6 +5226,9 @@
     <t>https://mcusercontent.com/695a3c121858dc1c6820969c0/files/c3885b8a-1ef9-ff8a-29e6-20a23a2e23fd/PAKISTAN_Preparedness_activities_report.pdf</t>
   </si>
   <si>
+    <t>National Society Preparedness - Introduction</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=w6RJt5WYfQw</t>
   </si>
   <si>
@@ -5008,6 +5271,9 @@
     <t>https://www.youtube.com/watch?v=AFvCMKisoRs&amp;feature=youtu.be</t>
   </si>
   <si>
+    <t>Technological and Biological Hazards</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=3XJVNhVmmCg</t>
   </si>
   <si>
@@ -5129,147 +5395,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=nDrFZ7mUd4w&amp;feature=youtu.be</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:b:/s/IFRCSharing/EXKvUpUXf09KrMRsJbjDMBYBgeq1VxRRYj-8h1ti1qP4lg</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:b:/s/IFRCSharing/EeIRNHF_ZfdHoXBjSyrXjYIBWLdOIunH4vlhj9zRxTdkig</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:b:/s/IFRCSharing/EbjrNJnBu1tAsdaDGU0Gn0MB1bdCRAeTb4nvdLJJLJIRnw?e=qTADTC</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:b:/s/IFRCSharing/EfxfkvNw8PBMkOVo_lTZXDwBY9VMjC5CLKqAkj8uUjJsYA?e=cUY1dT</t>
-  </si>
-  <si>
-    <t>https://www.ifrc.org/sites/default/files/2025-09/Marco%20para%20la%20preparaci%C3%B3n%20de%20las%20Sociedades%20Nacionales%20de%20IFRC.pdf</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>NSP Reference Materials</t>
-  </si>
-  <si>
-    <t>NSP Channels</t>
-  </si>
-  <si>
-    <t>PER Learning videos</t>
-  </si>
-  <si>
-    <t>Community of Practice</t>
-  </si>
-  <si>
-    <t>A more effective response is possible: Panama</t>
-  </si>
-  <si>
-    <t>PER Learning course</t>
-  </si>
-  <si>
-    <t>Success stories</t>
-  </si>
-  <si>
-    <t>The PER Approach</t>
-  </si>
-  <si>
-    <t>The PER Mechanism</t>
-  </si>
-  <si>
-    <t>NS Preparedness Framework</t>
-  </si>
-  <si>
-    <t>Core document</t>
-  </si>
-  <si>
-    <t>PER in the DRM Continuum</t>
-  </si>
-  <si>
-    <t>Rapid Response check</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgALVB8KXrLtSIzZ893caSBvATXkabA_iaFjdVVqjVVOFgI</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDwwnR3rmlsQ5b0RrGc3io8AXcHltgyPpuYbrnIQdR16-I</t>
-  </si>
-  <si>
-    <t>Learnings from operations</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBk1neqyK2uT7WmsyrWNp1ZAVxR5yhej2LOTY9nSz7lBDY</t>
-  </si>
-  <si>
-    <t>NSD-NSP</t>
-  </si>
-  <si>
-    <t>Linkages</t>
-  </si>
-  <si>
-    <t>Tools</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgBv7aZfU-IUQY9sAHIHlWJGAQmLAQgb_cGtGzR9AINCCwM</t>
-  </si>
-  <si>
-    <t>NS Preparedness links to key topics</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgCQuAdRTIMbToMpPI3hCw9dAcCbpFKHu0p_B9KQFTYa6ZQ</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgDvAlO3V1eQRbwBd6N9WFz3AY-xyajRbz_GrSrxr6uxrmU</t>
-  </si>
-  <si>
-    <t>Climate and environment</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgC0WXwnsUPRTLXWhNT8ATWpAS9ZYUacbW3o1pJsiRyPorg</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgB9EmeRgkHIR4xM-qYzby_3AVBirR01ho2SMgnUBD_Hyrc</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgB0-1YOM9aETIkHK1COoxvXAUKY7oK-YXIbzCFWedMsB-I</t>
-  </si>
-  <si>
-    <t>https://ifrcorg.sharepoint.com/:f:/s/IFRCSharing/IgASGMib140hQrhZQSdGSH9_AZzdh44KT20zkkWAfh_qmFQ</t>
-  </si>
-  <si>
-    <t>Popup</t>
-  </si>
-  <si>
-    <t>NS Preparedness links to Migration and Displacement</t>
-  </si>
-  <si>
-    <t>NS Preparedness links to Environmental and Climate</t>
-  </si>
-  <si>
-    <t>NS Preparedness links to PGI</t>
-  </si>
-  <si>
-    <t>NS Preparedness links to CEA</t>
-  </si>
-  <si>
-    <t>NS Preparedness links to Health</t>
-  </si>
-  <si>
-    <t>IFRC Webpage</t>
-  </si>
-  <si>
-    <t>to showcase experiences</t>
-  </si>
-  <si>
-    <t>NS Preparedness playlist</t>
-  </si>
-  <si>
-    <t>Quarterly published</t>
-  </si>
-  <si>
-    <t>NS Preparedness CoP</t>
-  </si>
-  <si>
-    <t>Channel</t>
   </si>
 </sst>
 </file>
@@ -6147,7 +6272,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6156,25 +6280,26 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -6205,9 +6330,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6245,7 +6370,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6351,7 +6476,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6493,7 +6618,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6502,24 +6627,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1FDDD64-0461-429D-8C62-D949FB27D80B}">
   <dimension ref="A1:S620"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="38.54296875" style="2" customWidth="1"/>
-    <col min="2" max="4" width="18.54296875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="35.453125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="36.54296875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.54296875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.1796875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" style="3" customWidth="1"/>
-    <col min="11" max="14" width="23.54296875" style="65" customWidth="1"/>
-    <col min="15" max="16" width="23.54296875" style="60" customWidth="1"/>
-    <col min="17" max="17" width="20.54296875" style="65" customWidth="1"/>
-    <col min="18" max="18" width="49.81640625" style="65" customWidth="1"/>
-    <col min="19" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="38.5703125" style="2" customWidth="1"/>
+    <col min="2" max="4" width="18.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="23.5703125" style="65" customWidth="1"/>
+    <col min="15" max="16" width="23.5703125" style="60" customWidth="1"/>
+    <col min="17" max="17" width="20.5703125" style="65" customWidth="1"/>
+    <col min="18" max="18" width="49.85546875" style="65" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="8" customFormat="1" ht="33.65" customHeight="1" thickBot="1">
+    <row r="1" spans="1:19" s="8" customFormat="1" ht="33.6" customHeight="1" thickBot="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -6546,7 +6671,7 @@
       <c r="R1" s="95"/>
       <c r="S1" s="97"/>
     </row>
-    <row r="2" spans="1:19" s="3" customFormat="1" ht="31">
+    <row r="2" spans="1:19" s="3" customFormat="1" ht="30.95">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -6655,7 +6780,7 @@
       </c>
       <c r="S3" s="97"/>
     </row>
-    <row r="4" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="4" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A4" s="99" t="s">
         <v>34</v>
       </c>
@@ -6689,7 +6814,7 @@
       <c r="R4" s="99"/>
       <c r="S4" s="97"/>
     </row>
-    <row r="5" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="5" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A5" s="16" t="s">
         <v>37</v>
       </c>
@@ -6735,7 +6860,7 @@
       <c r="R5" s="99"/>
       <c r="S5" s="97"/>
     </row>
-    <row r="6" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="6" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A6" s="99" t="s">
         <v>44</v>
       </c>
@@ -6777,7 +6902,7 @@
       <c r="R6" s="99"/>
       <c r="S6" s="97"/>
     </row>
-    <row r="7" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="7" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A7" s="99" t="s">
         <v>49</v>
       </c>
@@ -6831,7 +6956,7 @@
       </c>
       <c r="S7" s="97"/>
     </row>
-    <row r="8" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="8" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A8" s="99" t="s">
         <v>58</v>
       </c>
@@ -6881,7 +7006,7 @@
       </c>
       <c r="S8" s="97"/>
     </row>
-    <row r="9" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="9" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A9" s="99" t="s">
         <v>68</v>
       </c>
@@ -6923,7 +7048,7 @@
       <c r="R9" s="18"/>
       <c r="S9" s="97"/>
     </row>
-    <row r="10" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="10" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A10" s="99" t="s">
         <v>71</v>
       </c>
@@ -6961,7 +7086,7 @@
       <c r="R10" s="18"/>
       <c r="S10" s="97"/>
     </row>
-    <row r="11" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="11" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A11" s="16" t="s">
         <v>75</v>
       </c>
@@ -7015,7 +7140,7 @@
       </c>
       <c r="S11" s="97"/>
     </row>
-    <row r="12" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="12" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A12" s="16" t="s">
         <v>84</v>
       </c>
@@ -7137,7 +7262,7 @@
       <c r="R14" s="19"/>
       <c r="S14" s="97"/>
     </row>
-    <row r="15" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="15" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A15" s="99" t="s">
         <v>92</v>
       </c>
@@ -7275,7 +7400,7 @@
       <c r="R17" s="99"/>
       <c r="S17" s="97"/>
     </row>
-    <row r="18" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="18" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A18" s="99" t="s">
         <v>115</v>
       </c>
@@ -7377,7 +7502,7 @@
       <c r="R19" s="99"/>
       <c r="S19" s="97"/>
     </row>
-    <row r="20" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="20" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A20" s="99" t="s">
         <v>132</v>
       </c>
@@ -7421,7 +7546,7 @@
       <c r="R20" s="99"/>
       <c r="S20" s="97"/>
     </row>
-    <row r="21" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="21" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A21" s="99" t="s">
         <v>138</v>
       </c>
@@ -7473,7 +7598,7 @@
       <c r="R21" s="99"/>
       <c r="S21" s="97"/>
     </row>
-    <row r="22" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="22" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A22" s="99" t="s">
         <v>147</v>
       </c>
@@ -7619,7 +7744,7 @@
       <c r="R24" s="99"/>
       <c r="S24" s="97"/>
     </row>
-    <row r="25" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="25" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A25" s="99" t="s">
         <v>167</v>
       </c>
@@ -7719,7 +7844,7 @@
       <c r="R26" s="99"/>
       <c r="S26" s="97"/>
     </row>
-    <row r="27" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="27" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A27" s="99" t="s">
         <v>182</v>
       </c>
@@ -7885,7 +8010,7 @@
       <c r="R30" s="99"/>
       <c r="S30" s="97"/>
     </row>
-    <row r="31" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="31" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A31" s="99" t="s">
         <v>198</v>
       </c>
@@ -7931,7 +8056,7 @@
       <c r="R31" s="99"/>
       <c r="S31" s="97"/>
     </row>
-    <row r="32" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="32" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A32" s="99" t="s">
         <v>205</v>
       </c>
@@ -8301,7 +8426,7 @@
       <c r="R39" s="99"/>
       <c r="S39" s="97"/>
     </row>
-    <row r="40" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="40" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A40" s="99" t="s">
         <v>256</v>
       </c>
@@ -8351,7 +8476,7 @@
       <c r="R40" s="99"/>
       <c r="S40" s="97"/>
     </row>
-    <row r="41" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="41" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A41" s="99" t="s">
         <v>264</v>
       </c>
@@ -8435,7 +8560,7 @@
       </c>
       <c r="S42" s="97"/>
     </row>
-    <row r="43" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="43" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A43" s="99" t="s">
         <v>274</v>
       </c>
@@ -8613,7 +8738,7 @@
       </c>
       <c r="S46" s="97"/>
     </row>
-    <row r="47" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="47" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A47" s="99" t="s">
         <v>297</v>
       </c>
@@ -8645,7 +8770,7 @@
       <c r="R47" s="99"/>
       <c r="S47" s="97"/>
     </row>
-    <row r="48" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="48" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A48" s="99" t="s">
         <v>299</v>
       </c>
@@ -8675,7 +8800,7 @@
       <c r="R48" s="99"/>
       <c r="S48" s="97"/>
     </row>
-    <row r="49" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="49" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A49" s="99" t="s">
         <v>301</v>
       </c>
@@ -8751,7 +8876,7 @@
       <c r="R50" s="99"/>
       <c r="S50" s="97"/>
     </row>
-    <row r="51" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="51" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A51" s="99" t="s">
         <v>307</v>
       </c>
@@ -8793,7 +8918,7 @@
       <c r="R51" s="99"/>
       <c r="S51" s="97"/>
     </row>
-    <row r="52" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="52" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A52" s="105" t="s">
         <v>310</v>
       </c>
@@ -8837,7 +8962,7 @@
       <c r="R52" s="99"/>
       <c r="S52" s="97"/>
     </row>
-    <row r="53" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="53" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A53" s="99" t="s">
         <v>313</v>
       </c>
@@ -8879,7 +9004,7 @@
       <c r="R53" s="99"/>
       <c r="S53" s="97"/>
     </row>
-    <row r="54" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="54" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A54" s="99" t="s">
         <v>313</v>
       </c>
@@ -8921,7 +9046,7 @@
       <c r="R54" s="99"/>
       <c r="S54" s="97"/>
     </row>
-    <row r="55" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="55" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A55" s="99" t="s">
         <v>317</v>
       </c>
@@ -8971,7 +9096,7 @@
       <c r="R55" s="99"/>
       <c r="S55" s="97"/>
     </row>
-    <row r="56" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="56" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A56" s="99" t="s">
         <v>321</v>
       </c>
@@ -9051,7 +9176,7 @@
       <c r="R57" s="99"/>
       <c r="S57" s="97"/>
     </row>
-    <row r="58" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="58" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A58" s="99" t="s">
         <v>325</v>
       </c>
@@ -9091,7 +9216,7 @@
       <c r="R58" s="99"/>
       <c r="S58" s="97"/>
     </row>
-    <row r="59" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="59" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A59" s="99" t="s">
         <v>327</v>
       </c>
@@ -9139,7 +9264,7 @@
       <c r="R59" s="99"/>
       <c r="S59" s="97"/>
     </row>
-    <row r="60" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="60" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A60" s="99" t="s">
         <v>333</v>
       </c>
@@ -9179,7 +9304,7 @@
       <c r="R60" s="99"/>
       <c r="S60" s="97"/>
     </row>
-    <row r="61" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="61" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A61" s="99" t="s">
         <v>335</v>
       </c>
@@ -9219,7 +9344,7 @@
       <c r="R61" s="99"/>
       <c r="S61" s="97"/>
     </row>
-    <row r="62" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="62" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A62" s="99" t="s">
         <v>337</v>
       </c>
@@ -9289,7 +9414,7 @@
       <c r="R63" s="104"/>
       <c r="S63" s="97"/>
     </row>
-    <row r="64" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="64" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A64" s="99" t="s">
         <v>343</v>
       </c>
@@ -9369,7 +9494,7 @@
       <c r="R65" s="99"/>
       <c r="S65" s="97"/>
     </row>
-    <row r="66" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="66" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A66" s="99" t="s">
         <v>350</v>
       </c>
@@ -9509,7 +9634,7 @@
       <c r="R68" s="99"/>
       <c r="S68" s="97"/>
     </row>
-    <row r="69" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="69" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A69" s="99" t="s">
         <v>358</v>
       </c>
@@ -9633,7 +9758,7 @@
       <c r="R71" s="99"/>
       <c r="S71" s="97"/>
     </row>
-    <row r="72" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="72" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A72" s="99" t="s">
         <v>370</v>
       </c>
@@ -9685,7 +9810,7 @@
       <c r="R72" s="99"/>
       <c r="S72" s="97"/>
     </row>
-    <row r="73" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="73" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A73" s="4" t="s">
         <v>377</v>
       </c>
@@ -9729,7 +9854,7 @@
       <c r="R73" s="99"/>
       <c r="S73" s="97"/>
     </row>
-    <row r="74" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="74" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A74" s="16" t="s">
         <v>380</v>
       </c>
@@ -9773,7 +9898,7 @@
       <c r="R74" s="99"/>
       <c r="S74" s="97"/>
     </row>
-    <row r="75" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="75" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A75" s="16" t="s">
         <v>382</v>
       </c>
@@ -9817,7 +9942,7 @@
       <c r="R75" s="99"/>
       <c r="S75" s="97"/>
     </row>
-    <row r="76" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="76" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A76" s="16" t="s">
         <v>384</v>
       </c>
@@ -9861,7 +9986,7 @@
       <c r="R76" s="99"/>
       <c r="S76" s="97"/>
     </row>
-    <row r="77" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="77" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A77" s="16" t="s">
         <v>386</v>
       </c>
@@ -9905,7 +10030,7 @@
       <c r="R77" s="99"/>
       <c r="S77" s="97"/>
     </row>
-    <row r="78" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="78" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A78" s="16" t="s">
         <v>388</v>
       </c>
@@ -9949,7 +10074,7 @@
       <c r="R78" s="99"/>
       <c r="S78" s="97"/>
     </row>
-    <row r="79" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="79" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A79" s="16" t="s">
         <v>390</v>
       </c>
@@ -9993,7 +10118,7 @@
       <c r="R79" s="99"/>
       <c r="S79" s="97"/>
     </row>
-    <row r="80" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="80" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A80" s="38" t="s">
         <v>392</v>
       </c>
@@ -10035,7 +10160,7 @@
       <c r="R80" s="99"/>
       <c r="S80" s="97"/>
     </row>
-    <row r="81" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="81" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A81" s="16" t="s">
         <v>394</v>
       </c>
@@ -10079,7 +10204,7 @@
       <c r="R81" s="99"/>
       <c r="S81" s="97"/>
     </row>
-    <row r="82" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="82" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A82" s="39" t="s">
         <v>396</v>
       </c>
@@ -10121,7 +10246,7 @@
       <c r="R82" s="99"/>
       <c r="S82" s="97"/>
     </row>
-    <row r="83" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="83" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A83" s="16" t="s">
         <v>398</v>
       </c>
@@ -10165,7 +10290,7 @@
       <c r="R83" s="99"/>
       <c r="S83" s="97"/>
     </row>
-    <row r="84" spans="1:19" s="8" customFormat="1" ht="72.5">
+    <row r="84" spans="1:19" s="8" customFormat="1" ht="72.599999999999994">
       <c r="A84" s="16" t="s">
         <v>400</v>
       </c>
@@ -10209,7 +10334,7 @@
       <c r="R84" s="99"/>
       <c r="S84" s="97"/>
     </row>
-    <row r="85" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="85" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A85" s="16" t="s">
         <v>402</v>
       </c>
@@ -10253,7 +10378,7 @@
       <c r="R85" s="99"/>
       <c r="S85" s="97"/>
     </row>
-    <row r="86" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="86" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A86" s="16" t="s">
         <v>405</v>
       </c>
@@ -10297,7 +10422,7 @@
       <c r="R86" s="99"/>
       <c r="S86" s="97"/>
     </row>
-    <row r="87" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="87" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A87" s="16" t="s">
         <v>407</v>
       </c>
@@ -10347,7 +10472,7 @@
       <c r="R87" s="99"/>
       <c r="S87" s="97"/>
     </row>
-    <row r="88" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="88" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A88" s="24" t="s">
         <v>412</v>
       </c>
@@ -10389,7 +10514,7 @@
       <c r="R88" s="99"/>
       <c r="S88" s="97"/>
     </row>
-    <row r="89" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="89" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A89" s="99" t="s">
         <v>415</v>
       </c>
@@ -10479,7 +10604,7 @@
       <c r="R90" s="99"/>
       <c r="S90" s="97"/>
     </row>
-    <row r="91" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="91" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A91" s="99" t="s">
         <v>423</v>
       </c>
@@ -10525,7 +10650,7 @@
       <c r="R91" s="99"/>
       <c r="S91" s="97"/>
     </row>
-    <row r="92" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="92" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A92" s="99" t="s">
         <v>428</v>
       </c>
@@ -10611,7 +10736,7 @@
       <c r="R93" s="99"/>
       <c r="S93" s="97"/>
     </row>
-    <row r="94" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="94" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A94" s="99" t="s">
         <v>434</v>
       </c>
@@ -10651,7 +10776,7 @@
       <c r="R94" s="99"/>
       <c r="S94" s="97"/>
     </row>
-    <row r="95" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="95" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A95" s="99" t="s">
         <v>437</v>
       </c>
@@ -10787,7 +10912,7 @@
       <c r="R97" s="99"/>
       <c r="S97" s="97"/>
     </row>
-    <row r="98" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="98" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A98" s="99" t="s">
         <v>450</v>
       </c>
@@ -10827,7 +10952,7 @@
       <c r="R98" s="99"/>
       <c r="S98" s="97"/>
     </row>
-    <row r="99" spans="1:19" s="8" customFormat="1" ht="101.5">
+    <row r="99" spans="1:19" s="8" customFormat="1" ht="101.45">
       <c r="A99" s="99" t="s">
         <v>453</v>
       </c>
@@ -11005,7 +11130,7 @@
       <c r="R102" s="99"/>
       <c r="S102" s="97"/>
     </row>
-    <row r="103" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="103" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A103" s="99" t="s">
         <v>468</v>
       </c>
@@ -11087,7 +11212,7 @@
       <c r="R104" s="99"/>
       <c r="S104" s="97"/>
     </row>
-    <row r="105" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="105" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A105" s="99" t="s">
         <v>474</v>
       </c>
@@ -11133,7 +11258,7 @@
       </c>
       <c r="S105" s="97"/>
     </row>
-    <row r="106" spans="1:19" s="8" customFormat="1" ht="62.5">
+    <row r="106" spans="1:19" s="8" customFormat="1" ht="62.45">
       <c r="A106" s="105" t="s">
         <v>478</v>
       </c>
@@ -11183,7 +11308,7 @@
       <c r="R106" s="99"/>
       <c r="S106" s="97"/>
     </row>
-    <row r="107" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="107" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A107" s="99" t="s">
         <v>488</v>
       </c>
@@ -11267,7 +11392,7 @@
       <c r="R108" s="99"/>
       <c r="S108" s="97"/>
     </row>
-    <row r="109" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="109" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A109" s="106" t="s">
         <v>495</v>
       </c>
@@ -11315,7 +11440,7 @@
       <c r="R109" s="15"/>
       <c r="S109" s="97"/>
     </row>
-    <row r="110" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="110" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A110" s="107" t="s">
         <v>501</v>
       </c>
@@ -11411,7 +11536,7 @@
       <c r="R111" s="99"/>
       <c r="S111" s="97"/>
     </row>
-    <row r="112" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="112" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A112" s="99" t="s">
         <v>510</v>
       </c>
@@ -11449,7 +11574,7 @@
       <c r="R112" s="99"/>
       <c r="S112" s="97"/>
     </row>
-    <row r="113" spans="1:19" s="8" customFormat="1" ht="72.5">
+    <row r="113" spans="1:19" s="8" customFormat="1" ht="72.599999999999994">
       <c r="A113" s="99" t="s">
         <v>514</v>
       </c>
@@ -11495,7 +11620,7 @@
       <c r="R113" s="99"/>
       <c r="S113" s="97"/>
     </row>
-    <row r="114" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="114" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A114" s="99" t="s">
         <v>519</v>
       </c>
@@ -11537,7 +11662,7 @@
       <c r="R114" s="99"/>
       <c r="S114" s="97"/>
     </row>
-    <row r="115" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="115" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A115" s="99" t="s">
         <v>522</v>
       </c>
@@ -11613,7 +11738,7 @@
       <c r="R116" s="99"/>
       <c r="S116" s="97"/>
     </row>
-    <row r="117" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="117" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A117" s="99" t="s">
         <v>531</v>
       </c>
@@ -11709,7 +11834,7 @@
       <c r="R118" s="28"/>
       <c r="S118" s="97"/>
     </row>
-    <row r="119" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="119" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A119" s="99" t="s">
         <v>541</v>
       </c>
@@ -11753,7 +11878,7 @@
       <c r="R119" s="99"/>
       <c r="S119" s="97"/>
     </row>
-    <row r="120" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="120" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A120" s="99" t="s">
         <v>546</v>
       </c>
@@ -11801,7 +11926,7 @@
       </c>
       <c r="S120" s="97"/>
     </row>
-    <row r="121" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="121" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A121" s="97" t="s">
         <v>552</v>
       </c>
@@ -11839,7 +11964,7 @@
       <c r="R121" s="99"/>
       <c r="S121" s="97"/>
     </row>
-    <row r="122" spans="1:19" s="8" customFormat="1" ht="72.5">
+    <row r="122" spans="1:19" s="8" customFormat="1" ht="72.599999999999994">
       <c r="A122" s="99" t="s">
         <v>554</v>
       </c>
@@ -11879,7 +12004,7 @@
       <c r="R122" s="99"/>
       <c r="S122" s="97"/>
     </row>
-    <row r="123" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="123" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A123" s="99" t="s">
         <v>557</v>
       </c>
@@ -11921,7 +12046,7 @@
       <c r="R123" s="99"/>
       <c r="S123" s="97"/>
     </row>
-    <row r="124" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="124" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A124" s="99" t="s">
         <v>561</v>
       </c>
@@ -12015,7 +12140,7 @@
       <c r="R125" s="99"/>
       <c r="S125" s="97"/>
     </row>
-    <row r="126" spans="1:19" s="8" customFormat="1" ht="62.5">
+    <row r="126" spans="1:19" s="8" customFormat="1" ht="62.45">
       <c r="A126" s="99" t="s">
         <v>569</v>
       </c>
@@ -12117,7 +12242,7 @@
       </c>
       <c r="S127" s="97"/>
     </row>
-    <row r="128" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="128" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A128" s="97" t="s">
         <v>586</v>
       </c>
@@ -12159,7 +12284,7 @@
       <c r="R128" s="99"/>
       <c r="S128" s="97"/>
     </row>
-    <row r="129" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="129" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A129" s="99" t="s">
         <v>590</v>
       </c>
@@ -12203,7 +12328,7 @@
       </c>
       <c r="S129" s="97"/>
     </row>
-    <row r="130" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="130" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A130" s="99" t="s">
         <v>592</v>
       </c>
@@ -12241,7 +12366,7 @@
       </c>
       <c r="S130" s="97"/>
     </row>
-    <row r="131" spans="1:19" s="8" customFormat="1" ht="72.5">
+    <row r="131" spans="1:19" s="8" customFormat="1" ht="72.599999999999994">
       <c r="A131" s="99" t="s">
         <v>595</v>
       </c>
@@ -12285,7 +12410,7 @@
       </c>
       <c r="S131" s="97"/>
     </row>
-    <row r="132" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="132" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A132" s="34" t="s">
         <v>599</v>
       </c>
@@ -12327,7 +12452,7 @@
       <c r="R132" s="29"/>
       <c r="S132" s="97"/>
     </row>
-    <row r="133" spans="1:19" s="8" customFormat="1" ht="72.5">
+    <row r="133" spans="1:19" s="8" customFormat="1" ht="72.599999999999994">
       <c r="A133" s="99" t="s">
         <v>603</v>
       </c>
@@ -12369,7 +12494,7 @@
       </c>
       <c r="S133" s="97"/>
     </row>
-    <row r="134" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="134" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A134" s="99" t="s">
         <v>609</v>
       </c>
@@ -12593,7 +12718,7 @@
       <c r="R138" s="99"/>
       <c r="S138" s="97"/>
     </row>
-    <row r="139" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="139" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A139" s="99" t="s">
         <v>630</v>
       </c>
@@ -12635,7 +12760,7 @@
       <c r="R139" s="99"/>
       <c r="S139" s="97"/>
     </row>
-    <row r="140" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="140" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A140" s="16" t="s">
         <v>632</v>
       </c>
@@ -12679,7 +12804,7 @@
       <c r="R140" s="99"/>
       <c r="S140" s="97"/>
     </row>
-    <row r="141" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="141" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A141" s="99" t="s">
         <v>635</v>
       </c>
@@ -12723,7 +12848,7 @@
       <c r="R141" s="99"/>
       <c r="S141" s="97"/>
     </row>
-    <row r="142" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="142" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A142" s="99" t="s">
         <v>638</v>
       </c>
@@ -12763,7 +12888,7 @@
       <c r="R142" s="99"/>
       <c r="S142" s="97"/>
     </row>
-    <row r="143" spans="1:19" s="8" customFormat="1" ht="101.5">
+    <row r="143" spans="1:19" s="8" customFormat="1" ht="101.45">
       <c r="A143" s="107" t="s">
         <v>640</v>
       </c>
@@ -12811,7 +12936,7 @@
       </c>
       <c r="S143" s="97"/>
     </row>
-    <row r="144" spans="1:19" s="8" customFormat="1" ht="116">
+    <row r="144" spans="1:19" s="8" customFormat="1" ht="116.1">
       <c r="A144" s="107" t="s">
         <v>647</v>
       </c>
@@ -12859,7 +12984,7 @@
       </c>
       <c r="S144" s="97"/>
     </row>
-    <row r="145" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="145" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A145" s="99" t="s">
         <v>653</v>
       </c>
@@ -12905,7 +13030,7 @@
       <c r="R145" s="99"/>
       <c r="S145" s="97"/>
     </row>
-    <row r="146" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="146" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A146" s="99" t="s">
         <v>656</v>
       </c>
@@ -12949,7 +13074,7 @@
       <c r="R146" s="99"/>
       <c r="S146" s="97"/>
     </row>
-    <row r="147" spans="1:19" s="8" customFormat="1" ht="72.5">
+    <row r="147" spans="1:19" s="8" customFormat="1" ht="72.599999999999994">
       <c r="A147" s="99" t="s">
         <v>658</v>
       </c>
@@ -13071,7 +13196,7 @@
       <c r="R149" s="99"/>
       <c r="S149" s="97"/>
     </row>
-    <row r="150" spans="1:19" s="8" customFormat="1" ht="44" thickBot="1">
+    <row r="150" spans="1:19" s="8" customFormat="1" ht="44.1" thickBot="1">
       <c r="A150" s="99" t="s">
         <v>668</v>
       </c>
@@ -13239,7 +13364,7 @@
       <c r="R153" s="107"/>
       <c r="S153" s="97"/>
     </row>
-    <row r="154" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="154" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A154" s="32" t="s">
         <v>687</v>
       </c>
@@ -13323,7 +13448,7 @@
       <c r="R155" s="107"/>
       <c r="S155" s="97"/>
     </row>
-    <row r="156" spans="1:19" s="8" customFormat="1" ht="50.5" thickBot="1">
+    <row r="156" spans="1:19" s="8" customFormat="1" ht="50.45" thickBot="1">
       <c r="A156" s="32" t="s">
         <v>697</v>
       </c>
@@ -13535,7 +13660,7 @@
       <c r="R160" s="107"/>
       <c r="S160" s="97"/>
     </row>
-    <row r="161" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="161" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A161" s="32" t="s">
         <v>723</v>
       </c>
@@ -13619,7 +13744,7 @@
       <c r="R162" s="107"/>
       <c r="S162" s="97"/>
     </row>
-    <row r="163" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="163" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A163" s="32" t="s">
         <v>733</v>
       </c>
@@ -13955,7 +14080,7 @@
       <c r="R170" s="107"/>
       <c r="S170" s="97"/>
     </row>
-    <row r="171" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="171" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A171" s="32" t="s">
         <v>776</v>
       </c>
@@ -14039,7 +14164,7 @@
       <c r="R172" s="107"/>
       <c r="S172" s="97"/>
     </row>
-    <row r="173" spans="1:19" s="8" customFormat="1" ht="50.5" thickBot="1">
+    <row r="173" spans="1:19" s="8" customFormat="1" ht="50.45" thickBot="1">
       <c r="A173" s="32" t="s">
         <v>787</v>
       </c>
@@ -14249,7 +14374,7 @@
       <c r="R177" s="107"/>
       <c r="S177" s="97"/>
     </row>
-    <row r="178" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="178" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A178" s="32" t="s">
         <v>814</v>
       </c>
@@ -14505,7 +14630,7 @@
       <c r="R183" s="107"/>
       <c r="S183" s="97"/>
     </row>
-    <row r="184" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="184" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A184" s="32" t="s">
         <v>845</v>
       </c>
@@ -14631,7 +14756,7 @@
       <c r="R186" s="107"/>
       <c r="S186" s="97"/>
     </row>
-    <row r="187" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="187" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A187" s="32" t="s">
         <v>860</v>
       </c>
@@ -14757,7 +14882,7 @@
       <c r="R189" s="107"/>
       <c r="S189" s="97"/>
     </row>
-    <row r="190" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="190" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A190" s="32" t="s">
         <v>876</v>
       </c>
@@ -14843,7 +14968,7 @@
       <c r="R191" s="109"/>
       <c r="S191" s="97"/>
     </row>
-    <row r="192" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="192" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A192" s="32" t="s">
         <v>887</v>
       </c>
@@ -14971,7 +15096,7 @@
       <c r="R194" s="107"/>
       <c r="S194" s="97"/>
     </row>
-    <row r="195" spans="1:19" s="8" customFormat="1" ht="50.5" thickBot="1">
+    <row r="195" spans="1:19" s="8" customFormat="1" ht="50.45" thickBot="1">
       <c r="A195" s="32" t="s">
         <v>904</v>
       </c>
@@ -15013,7 +15138,7 @@
       <c r="R195" s="107"/>
       <c r="S195" s="97"/>
     </row>
-    <row r="196" spans="1:19" s="8" customFormat="1" ht="50.5" thickBot="1">
+    <row r="196" spans="1:19" s="8" customFormat="1" ht="50.45" thickBot="1">
       <c r="A196" s="32" t="s">
         <v>909</v>
       </c>
@@ -15055,7 +15180,7 @@
       <c r="R196" s="107"/>
       <c r="S196" s="97"/>
     </row>
-    <row r="197" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="197" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A197" s="32" t="s">
         <v>914</v>
       </c>
@@ -15097,7 +15222,7 @@
       <c r="R197" s="107"/>
       <c r="S197" s="97"/>
     </row>
-    <row r="198" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="198" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A198" s="32" t="s">
         <v>920</v>
       </c>
@@ -15139,7 +15264,7 @@
       <c r="R198" s="107"/>
       <c r="S198" s="97"/>
     </row>
-    <row r="199" spans="1:19" s="8" customFormat="1" ht="38" thickBot="1">
+    <row r="199" spans="1:19" s="8" customFormat="1" ht="38.1" thickBot="1">
       <c r="A199" s="32" t="s">
         <v>925</v>
       </c>
@@ -15267,7 +15392,7 @@
       <c r="R201" s="107"/>
       <c r="S201" s="97"/>
     </row>
-    <row r="202" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="202" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A202" s="107" t="s">
         <v>940</v>
       </c>
@@ -15309,7 +15434,7 @@
       <c r="R202" s="107"/>
       <c r="S202" s="97"/>
     </row>
-    <row r="203" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="203" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A203" s="99" t="s">
         <v>942</v>
       </c>
@@ -15351,7 +15476,7 @@
       <c r="R203" s="107"/>
       <c r="S203" s="97"/>
     </row>
-    <row r="204" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="204" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A204" s="99" t="s">
         <v>944</v>
       </c>
@@ -15437,7 +15562,7 @@
       <c r="R205" s="107"/>
       <c r="S205" s="97"/>
     </row>
-    <row r="206" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="206" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A206" s="16" t="s">
         <v>949</v>
       </c>
@@ -15483,7 +15608,7 @@
       <c r="R206" s="107"/>
       <c r="S206" s="97"/>
     </row>
-    <row r="207" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="207" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A207" s="99" t="s">
         <v>954</v>
       </c>
@@ -15527,7 +15652,7 @@
       <c r="R207" s="107"/>
       <c r="S207" s="97"/>
     </row>
-    <row r="208" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="208" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A208" s="99" t="s">
         <v>956</v>
       </c>
@@ -15615,7 +15740,7 @@
       <c r="R209" s="109"/>
       <c r="S209" s="97"/>
     </row>
-    <row r="210" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="210" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A210" s="99" t="s">
         <v>963</v>
       </c>
@@ -15715,7 +15840,7 @@
       <c r="R211" s="99"/>
       <c r="S211" s="97"/>
     </row>
-    <row r="212" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="212" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A212" s="104" t="s">
         <v>977</v>
       </c>
@@ -15765,7 +15890,7 @@
       <c r="R212" s="99"/>
       <c r="S212" s="97"/>
     </row>
-    <row r="213" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="213" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A213" s="16" t="s">
         <v>982</v>
       </c>
@@ -15809,7 +15934,7 @@
       <c r="R213" s="99"/>
       <c r="S213" s="97"/>
     </row>
-    <row r="214" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="214" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A214" s="16" t="s">
         <v>985</v>
       </c>
@@ -15853,7 +15978,7 @@
       <c r="R214" s="99"/>
       <c r="S214" s="97"/>
     </row>
-    <row r="215" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="215" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A215" s="99" t="s">
         <v>988</v>
       </c>
@@ -15897,7 +16022,7 @@
       <c r="R215" s="99"/>
       <c r="S215" s="97"/>
     </row>
-    <row r="216" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="216" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A216" s="99" t="s">
         <v>991</v>
       </c>
@@ -15939,7 +16064,7 @@
       </c>
       <c r="S216" s="97"/>
     </row>
-    <row r="217" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="217" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A217" s="99" t="s">
         <v>994</v>
       </c>
@@ -16099,7 +16224,7 @@
       <c r="R220" s="107"/>
       <c r="S220" s="97"/>
     </row>
-    <row r="221" spans="1:19" s="8" customFormat="1" ht="62.5">
+    <row r="221" spans="1:19" s="8" customFormat="1" ht="62.45">
       <c r="A221" s="99" t="s">
         <v>1004</v>
       </c>
@@ -16277,7 +16402,7 @@
       <c r="R224" s="99"/>
       <c r="S224" s="97"/>
     </row>
-    <row r="225" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="225" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A225" s="99" t="s">
         <v>1020</v>
       </c>
@@ -16329,7 +16454,7 @@
       </c>
       <c r="S225" s="97"/>
     </row>
-    <row r="226" spans="1:19" s="8" customFormat="1" ht="72.5">
+    <row r="226" spans="1:19" s="8" customFormat="1" ht="72.599999999999994">
       <c r="A226" s="99" t="s">
         <v>1028</v>
       </c>
@@ -16375,7 +16500,7 @@
       <c r="R226" s="99"/>
       <c r="S226" s="97"/>
     </row>
-    <row r="227" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="227" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A227" s="107" t="s">
         <v>1032</v>
       </c>
@@ -16545,7 +16670,7 @@
       <c r="R230" s="107"/>
       <c r="S230" s="97"/>
     </row>
-    <row r="231" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="231" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A231" s="99" t="s">
         <v>1047</v>
       </c>
@@ -16589,7 +16714,7 @@
       <c r="R231" s="99"/>
       <c r="S231" s="97"/>
     </row>
-    <row r="232" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="232" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A232" s="107" t="s">
         <v>1051</v>
       </c>
@@ -16633,7 +16758,7 @@
       <c r="R232" s="107"/>
       <c r="S232" s="97"/>
     </row>
-    <row r="233" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="233" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A233" s="107" t="s">
         <v>1054</v>
       </c>
@@ -16673,7 +16798,7 @@
       <c r="R233" s="107"/>
       <c r="S233" s="97"/>
     </row>
-    <row r="234" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="234" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A234" s="107" t="s">
         <v>1056</v>
       </c>
@@ -16885,7 +17010,7 @@
       <c r="R238" s="107"/>
       <c r="S238" s="97"/>
     </row>
-    <row r="239" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="239" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A239" s="107" t="s">
         <v>1076</v>
       </c>
@@ -17123,7 +17248,7 @@
       <c r="R244" s="107"/>
       <c r="S244" s="97"/>
     </row>
-    <row r="245" spans="1:19" s="8" customFormat="1" ht="25">
+    <row r="245" spans="1:19" s="8" customFormat="1" ht="24.95">
       <c r="A245" s="107" t="s">
         <v>1091</v>
       </c>
@@ -17171,7 +17296,7 @@
       </c>
       <c r="S245" s="97"/>
     </row>
-    <row r="246" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="246" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A246" s="107" t="s">
         <v>1098</v>
       </c>
@@ -17215,7 +17340,7 @@
       <c r="R246" s="107"/>
       <c r="S246" s="97"/>
     </row>
-    <row r="247" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="247" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A247" s="107" t="s">
         <v>1103</v>
       </c>
@@ -17303,7 +17428,7 @@
       <c r="R248" s="107"/>
       <c r="S248" s="97"/>
     </row>
-    <row r="249" spans="1:19" s="8" customFormat="1" ht="72.5">
+    <row r="249" spans="1:19" s="8" customFormat="1" ht="72.599999999999994">
       <c r="A249" s="107" t="s">
         <v>1112</v>
       </c>
@@ -17433,7 +17558,7 @@
       <c r="R251" s="107"/>
       <c r="S251" s="97"/>
     </row>
-    <row r="252" spans="1:19" s="8" customFormat="1" ht="101.5">
+    <row r="252" spans="1:19" s="8" customFormat="1" ht="101.45">
       <c r="A252" s="107" t="s">
         <v>1121</v>
       </c>
@@ -17523,7 +17648,7 @@
       <c r="R253" s="107"/>
       <c r="S253" s="97"/>
     </row>
-    <row r="254" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="254" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A254" s="107" t="s">
         <v>1130</v>
       </c>
@@ -17645,7 +17770,7 @@
       <c r="R256" s="107"/>
       <c r="S256" s="97"/>
     </row>
-    <row r="257" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="257" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A257" s="107" t="s">
         <v>1138</v>
       </c>
@@ -17685,7 +17810,7 @@
       <c r="R257" s="107"/>
       <c r="S257" s="97"/>
     </row>
-    <row r="258" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="258" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A258" s="107" t="s">
         <v>1142</v>
       </c>
@@ -17725,7 +17850,7 @@
       <c r="R258" s="107"/>
       <c r="S258" s="97"/>
     </row>
-    <row r="259" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="259" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A259" s="107" t="s">
         <v>1144</v>
       </c>
@@ -17809,7 +17934,7 @@
       <c r="R260" s="107"/>
       <c r="S260" s="97"/>
     </row>
-    <row r="261" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="261" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A261" s="107" t="s">
         <v>1149</v>
       </c>
@@ -17861,7 +17986,7 @@
       <c r="R261" s="107"/>
       <c r="S261" s="97"/>
     </row>
-    <row r="262" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="262" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A262" s="107" t="s">
         <v>1156</v>
       </c>
@@ -17909,7 +18034,7 @@
       <c r="R262" s="107"/>
       <c r="S262" s="97"/>
     </row>
-    <row r="263" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="263" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A263" s="42" t="s">
         <v>1158</v>
       </c>
@@ -17955,7 +18080,7 @@
       <c r="R263" s="107"/>
       <c r="S263" s="97"/>
     </row>
-    <row r="264" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="264" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A264" s="41" t="s">
         <v>1162</v>
       </c>
@@ -18005,7 +18130,7 @@
       <c r="R264" s="107"/>
       <c r="S264" s="97"/>
     </row>
-    <row r="265" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="265" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A265" s="43" t="s">
         <v>1167</v>
       </c>
@@ -18055,7 +18180,7 @@
       <c r="R265" s="107"/>
       <c r="S265" s="97"/>
     </row>
-    <row r="266" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="266" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A266" s="107" t="s">
         <v>1172</v>
       </c>
@@ -18141,7 +18266,7 @@
       <c r="R267" s="107"/>
       <c r="S267" s="97"/>
     </row>
-    <row r="268" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="268" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A268" s="107" t="s">
         <v>1178</v>
       </c>
@@ -18183,7 +18308,7 @@
       <c r="R268" s="107"/>
       <c r="S268" s="97"/>
     </row>
-    <row r="269" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="269" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A269" s="107" t="s">
         <v>1181</v>
       </c>
@@ -18269,7 +18394,7 @@
       <c r="R270" s="107"/>
       <c r="S270" s="97"/>
     </row>
-    <row r="271" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="271" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A271" s="107" t="s">
         <v>1187</v>
       </c>
@@ -18319,7 +18444,7 @@
       <c r="R271" s="107"/>
       <c r="S271" s="97"/>
     </row>
-    <row r="272" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="272" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A272" s="107" t="s">
         <v>1193</v>
       </c>
@@ -18451,7 +18576,7 @@
       <c r="R274" s="107"/>
       <c r="S274" s="97"/>
     </row>
-    <row r="275" spans="1:19" s="8" customFormat="1" ht="29">
+    <row r="275" spans="1:19" s="8" customFormat="1" ht="29.1">
       <c r="A275" s="107" t="s">
         <v>1210</v>
       </c>
@@ -18633,7 +18758,7 @@
       <c r="R278" s="107"/>
       <c r="S278" s="97"/>
     </row>
-    <row r="279" spans="1:19" s="8" customFormat="1" ht="50">
+    <row r="279" spans="1:19" s="8" customFormat="1" ht="50.1">
       <c r="A279" s="107" t="s">
         <v>1224</v>
       </c>
@@ -18924,7 +19049,7 @@
       <c r="R285" s="107"/>
       <c r="S285" s="118"/>
     </row>
-    <row r="286" spans="1:19" ht="58">
+    <row r="286" spans="1:19" ht="57.95">
       <c r="A286" s="107" t="s">
         <v>1254</v>
       </c>
@@ -19202,7 +19327,7 @@
       <c r="R292" s="107"/>
       <c r="S292" s="118"/>
     </row>
-    <row r="293" spans="1:19" ht="29">
+    <row r="293" spans="1:19" ht="29.1">
       <c r="A293" s="107" t="s">
         <v>1274</v>
       </c>
@@ -19330,7 +19455,7 @@
       <c r="R295" s="107"/>
       <c r="S295" s="118"/>
     </row>
-    <row r="296" spans="1:19" ht="50">
+    <row r="296" spans="1:19" ht="50.1">
       <c r="A296" s="107" t="s">
         <v>1283</v>
       </c>
@@ -19646,7 +19771,7 @@
       <c r="R303" s="107"/>
       <c r="S303" s="118"/>
     </row>
-    <row r="304" spans="1:19" ht="29">
+    <row r="304" spans="1:19" ht="29.1">
       <c r="A304" s="107" t="s">
         <v>1303</v>
       </c>
@@ -20186,7 +20311,7 @@
       <c r="R316" s="107"/>
       <c r="S316" s="118"/>
     </row>
-    <row r="317" spans="1:19" ht="58">
+    <row r="317" spans="1:19" ht="57.95">
       <c r="A317" s="107" t="s">
         <v>1340</v>
       </c>
@@ -20222,7 +20347,7 @@
       <c r="R317" s="107"/>
       <c r="S317" s="118"/>
     </row>
-    <row r="318" spans="1:19" ht="62.5">
+    <row r="318" spans="1:19" ht="62.45">
       <c r="A318" s="107" t="s">
         <v>1342</v>
       </c>
@@ -20514,7 +20639,7 @@
       <c r="R324" s="107"/>
       <c r="S324" s="118"/>
     </row>
-    <row r="325" spans="1:19" ht="29">
+    <row r="325" spans="1:19" ht="29.1">
       <c r="A325" s="107" t="s">
         <v>1360</v>
       </c>
@@ -20558,7 +20683,7 @@
       <c r="R325" s="107"/>
       <c r="S325" s="118"/>
     </row>
-    <row r="326" spans="1:19" ht="29">
+    <row r="326" spans="1:19" ht="29.1">
       <c r="A326" s="107" t="s">
         <v>1363</v>
       </c>
@@ -20792,7 +20917,7 @@
       <c r="R331" s="107"/>
       <c r="S331" s="118"/>
     </row>
-    <row r="332" spans="1:19" ht="25">
+    <row r="332" spans="1:19" ht="24.95">
       <c r="A332" s="107" t="s">
         <v>1378</v>
       </c>
@@ -20949,7 +21074,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="335" spans="1:19" ht="26">
+    <row r="335" spans="1:19" ht="26.1">
       <c r="A335" s="52" t="s">
         <v>1395</v>
       </c>
@@ -21067,7 +21192,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="337" spans="1:19" s="8" customFormat="1" ht="58">
+    <row r="337" spans="1:19" s="8" customFormat="1" ht="57.95">
       <c r="A337" s="16" t="s">
         <v>1402</v>
       </c>
@@ -21115,7 +21240,7 @@
       <c r="R337" s="19"/>
       <c r="S337" s="97"/>
     </row>
-    <row r="338" spans="1:19" ht="58">
+    <row r="338" spans="1:19" ht="57.95">
       <c r="A338" s="99" t="s">
         <v>1405</v>
       </c>
@@ -21157,7 +21282,7 @@
       <c r="R338" s="99"/>
       <c r="S338" s="97"/>
     </row>
-    <row r="339" spans="1:19" ht="29">
+    <row r="339" spans="1:19" ht="29.1">
       <c r="A339" s="99" t="s">
         <v>1407</v>
       </c>
@@ -28517,14 +28642,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46310129-492E-4576-B59B-9BA243D11E8E}">
   <dimension ref="A1:D53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="72.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="1.54296875" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="72.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13">
+    <row r="1" spans="1:4" ht="12.95">
       <c r="A1" s="1" t="s">
         <v>1421</v>
       </c>
@@ -28644,7 +28769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="13">
+    <row r="16" spans="1:4" ht="12.95">
       <c r="A16" t="s">
         <v>750</v>
       </c>
@@ -28861,142 +28986,142 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B429101-4D04-4B6C-A952-0AD12E543450}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="33.36328125" style="132" customWidth="1"/>
-    <col min="2" max="2" width="36.81640625" customWidth="1"/>
-    <col min="3" max="6" width="8.453125" style="134" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" style="132" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="6" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="133" customFormat="1" ht="26">
+    <row r="1" spans="1:6" s="133" customFormat="1" ht="26.1">
       <c r="A1" s="133" t="s">
-        <v>1447</v>
+        <v>1431</v>
       </c>
       <c r="B1" s="133" t="s">
-        <v>1446</v>
+        <v>1432</v>
       </c>
       <c r="C1" s="133" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="D1" s="133" t="s">
-        <v>1443</v>
+        <v>1434</v>
       </c>
       <c r="E1" s="133" t="s">
-        <v>1442</v>
+        <v>1435</v>
       </c>
       <c r="F1" s="133" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="132" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>1448</v>
+        <v>1438</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>1448</v>
+        <v>1438</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>1448</v>
+        <v>1438</v>
       </c>
       <c r="F2" s="68" t="s">
-        <v>1448</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="132" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="C3" s="68" t="s">
-        <v>1449</v>
+        <v>1440</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>1450</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="132" t="s">
-        <v>1434</v>
+        <v>1442</v>
       </c>
       <c r="C4" s="68" t="s">
-        <v>1455</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="132" t="s">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="C5" s="68" t="s">
-        <v>1454</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="132" t="s">
-        <v>1431</v>
+        <v>1446</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="132" t="s">
-        <v>1432</v>
+        <v>1449</v>
       </c>
       <c r="C7" s="68" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="24.95">
+      <c r="A8" s="132" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E8" s="68" t="s">
         <v>1453</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="134" customFormat="1" ht="25">
-      <c r="A8" s="132" t="s">
-        <v>1457</v>
-      </c>
-      <c r="C8" s="68" t="s">
-        <v>1456</v>
-      </c>
-      <c r="E8" s="68" t="s">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="134" customFormat="1">
+    <row r="9" spans="1:6">
       <c r="A9" s="132" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="C9" s="68"/>
     </row>
-    <row r="10" spans="1:6" s="134" customFormat="1">
+    <row r="10" spans="1:6">
       <c r="A10" s="132" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="C10" s="68"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="132" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="37.5">
       <c r="A13" s="132" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="132" t="s">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="25">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="24.95">
       <c r="A15" s="132" t="s">
-        <v>1437</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="132" t="s">
-        <v>1438</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -29011,7 +29136,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="132" t="s">
-        <v>1439</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -29026,7 +29151,7 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="132" t="s">
-        <v>1440</v>
+        <v>1462</v>
       </c>
     </row>
   </sheetData>
@@ -29051,1996 +29176,2078 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5274E520-0DCC-4EC6-A7BF-2432E418040B}">
-  <dimension ref="A1:M77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="12.5"/>
+  <dimension ref="A1:M78"/>
+  <sheetFormatPr defaultColWidth="12" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="22.08984375" style="134" customWidth="1"/>
-    <col min="2" max="2" width="12.90625" style="134" customWidth="1"/>
-    <col min="3" max="3" width="40" style="134" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" style="134" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" style="134" customWidth="1"/>
-    <col min="6" max="6" width="6.08984375" style="137" customWidth="1"/>
-    <col min="7" max="13" width="9.36328125" style="134" customWidth="1"/>
-    <col min="14" max="16384" width="12" style="134"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" style="136" customWidth="1"/>
+    <col min="7" max="13" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="139" customFormat="1" ht="14">
-      <c r="A1" s="138" t="s">
+    <row r="1" spans="1:13" s="138" customFormat="1" ht="14.1">
+      <c r="A1" s="137" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B1" s="137" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C1" s="137" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D1" s="137" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E1" s="137" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F1" s="137" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="137" t="s">
+        <v>1468</v>
+      </c>
+      <c r="H1" s="137" t="s">
+        <v>1469</v>
+      </c>
+      <c r="I1" s="137" t="s">
+        <v>1470</v>
+      </c>
+      <c r="J1" s="137" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K1" s="137" t="s">
+        <v>1472</v>
+      </c>
+      <c r="L1" s="137" t="s">
+        <v>1473</v>
+      </c>
+      <c r="M1" s="137" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="138" customFormat="1" ht="12.95">
+      <c r="A2" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B2" s="140" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C2" s="140" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="135" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H2" s="135" t="s">
+        <v>1478</v>
+      </c>
+      <c r="I2" s="135" t="s">
+        <v>1301</v>
+      </c>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+    </row>
+    <row r="3" spans="1:13" s="138" customFormat="1" ht="12.95">
+      <c r="A3" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B3" s="140" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C3" s="140" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="135" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H3" s="134" t="s">
+        <v>1481</v>
+      </c>
+      <c r="I3" s="134" t="s">
+        <v>1228</v>
+      </c>
+      <c r="J3" s="134" t="s">
+        <v>1482</v>
+      </c>
+      <c r="K3" s="135"/>
+      <c r="L3" s="135"/>
+      <c r="M3" s="135"/>
+    </row>
+    <row r="4" spans="1:13" s="142" customFormat="1">
+      <c r="A4" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B4" s="140" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C4" s="140" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="134" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H4" s="134" t="s">
+        <v>1235</v>
+      </c>
+      <c r="I4" s="134" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J4" s="134" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B5" s="140" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C5" s="140" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="134" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H5" s="134" t="s">
+        <v>1486</v>
+      </c>
+      <c r="I5" s="134" t="s">
+        <v>1487</v>
+      </c>
+      <c r="J5" s="134" t="s">
+        <v>1488</v>
+      </c>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+    </row>
+    <row r="6" spans="1:13" s="142" customFormat="1">
+      <c r="A6" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B6" s="140"/>
+      <c r="C6" s="140" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="135" t="s">
+        <v>1490</v>
+      </c>
+      <c r="H6" s="135" t="s">
+        <v>1491</v>
+      </c>
+      <c r="I6" s="135" t="s">
+        <v>1492</v>
+      </c>
+      <c r="J6" s="135" t="s">
+        <v>1493</v>
+      </c>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="140"/>
+    </row>
+    <row r="7" spans="1:13" s="142" customFormat="1">
+      <c r="A7" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B7" s="140"/>
+      <c r="C7" s="140" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="141"/>
+      <c r="G7" s="134" t="s">
+        <v>1495</v>
+      </c>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="140"/>
+    </row>
+    <row r="8" spans="1:13" s="142" customFormat="1">
+      <c r="A8" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B8" s="140"/>
+      <c r="C8" s="140" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="134" t="s">
+        <v>1497</v>
+      </c>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="140"/>
+    </row>
+    <row r="9" spans="1:13" s="142" customFormat="1">
+      <c r="A9" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B9" s="140"/>
+      <c r="C9" s="140" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="135" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H9" s="135" t="s">
+        <v>1500</v>
+      </c>
+      <c r="I9" s="135" t="s">
+        <v>1501</v>
+      </c>
+      <c r="J9" s="135" t="s">
+        <v>1502</v>
+      </c>
+      <c r="K9" s="140"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="140"/>
+    </row>
+    <row r="10" spans="1:13" s="142" customFormat="1">
+      <c r="A10" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B10" s="140" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C10" s="140" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D10" s="140"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="134" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H10" s="135" t="s">
+        <v>1505</v>
+      </c>
+      <c r="I10" s="135" t="s">
+        <v>1506</v>
+      </c>
+      <c r="J10" s="135" t="s">
+        <v>1507</v>
+      </c>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+    </row>
+    <row r="11" spans="1:13" s="142" customFormat="1">
+      <c r="A11" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B11" s="140" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C11" s="140" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="134" t="s">
+        <v>1509</v>
+      </c>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="140"/>
+      <c r="M11" s="140"/>
+    </row>
+    <row r="12" spans="1:13" s="142" customFormat="1">
+      <c r="A12" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B12" s="140" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C12" s="140" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="141"/>
+      <c r="G12" s="134" t="s">
+        <v>1511</v>
+      </c>
+      <c r="H12" s="134" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I12" s="134" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J12" s="134" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K12" s="134" t="s">
+        <v>1231</v>
+      </c>
+      <c r="L12" s="140"/>
+      <c r="M12" s="140"/>
+    </row>
+    <row r="13" spans="1:13" s="142" customFormat="1">
+      <c r="A13" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B13" s="140" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C13" s="140" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="141"/>
+      <c r="G13" s="134" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H13" s="135" t="s">
+        <v>1515</v>
+      </c>
+      <c r="I13" s="135" t="s">
+        <v>1516</v>
+      </c>
+      <c r="J13" s="135" t="s">
+        <v>1517</v>
+      </c>
+      <c r="K13" s="140"/>
+      <c r="L13" s="140"/>
+      <c r="M13" s="140"/>
+    </row>
+    <row r="14" spans="1:13" s="142" customFormat="1">
+      <c r="A14" s="139" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B14" s="143" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C14" s="143" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D14" s="143"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="134" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="140"/>
+      <c r="M14" s="140"/>
+    </row>
+    <row r="15" spans="1:13" s="142" customFormat="1">
+      <c r="A15" s="139" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B15" s="143" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C15" s="143" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D15" s="143"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="135" t="s">
+        <v>1523</v>
+      </c>
+      <c r="H15" s="140"/>
+      <c r="I15" s="140"/>
+      <c r="J15" s="140"/>
+      <c r="K15" s="140"/>
+      <c r="L15" s="140"/>
+      <c r="M15" s="140"/>
+    </row>
+    <row r="16" spans="1:13" s="142" customFormat="1">
+      <c r="A16" s="139" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B16" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C16" s="140" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="135" t="s">
+        <v>1525</v>
+      </c>
+      <c r="H16" s="140"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="140"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="140"/>
+    </row>
+    <row r="17" spans="1:13" s="142" customFormat="1">
+      <c r="A17" s="139" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B17" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C17" s="140" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D17" s="140"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="135" t="s">
+        <v>1527</v>
+      </c>
+      <c r="H17" s="140"/>
+      <c r="I17" s="140"/>
+      <c r="J17" s="140"/>
+      <c r="K17" s="140"/>
+      <c r="L17" s="140"/>
+      <c r="M17" s="140"/>
+    </row>
+    <row r="18" spans="1:13" s="142" customFormat="1">
+      <c r="A18" s="139" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B18" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C18" s="140" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D18" s="140"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="141"/>
+      <c r="G18" s="135" t="s">
+        <v>1529</v>
+      </c>
+      <c r="H18" s="140"/>
+      <c r="I18" s="140"/>
+      <c r="J18" s="140"/>
+      <c r="K18" s="140"/>
+      <c r="L18" s="140"/>
+      <c r="M18" s="140"/>
+    </row>
+    <row r="19" spans="1:13" s="142" customFormat="1">
+      <c r="A19" s="139" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B19" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C19" s="140" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D19" s="140"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="135" t="s">
+        <v>1531</v>
+      </c>
+      <c r="H19" s="140"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="140"/>
+      <c r="K19" s="140"/>
+      <c r="L19" s="140"/>
+      <c r="M19" s="140"/>
+    </row>
+    <row r="20" spans="1:13" s="142" customFormat="1">
+      <c r="A20" s="139" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B20" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C20" s="140" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="135" t="s">
+        <v>1533</v>
+      </c>
+      <c r="H20" s="140"/>
+      <c r="I20" s="140"/>
+      <c r="J20" s="140"/>
+      <c r="K20" s="140"/>
+      <c r="L20" s="140"/>
+      <c r="M20" s="140"/>
+    </row>
+    <row r="21" spans="1:13" s="142" customFormat="1">
+      <c r="A21" s="139" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B21" s="139"/>
+      <c r="C21" s="139" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D21" s="139"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="140"/>
+      <c r="J21" s="140"/>
+      <c r="K21" s="140"/>
+      <c r="L21" s="140"/>
+      <c r="M21" s="140"/>
+    </row>
+    <row r="22" spans="1:13" s="142" customFormat="1">
+      <c r="A22" s="139" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B22" s="139"/>
+      <c r="C22" s="139" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D22" s="139"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="140"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="140"/>
+    </row>
+    <row r="23" spans="1:13" s="142" customFormat="1">
+      <c r="A23" s="139" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B23" s="139"/>
+      <c r="C23" s="139" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D23" s="139"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="140"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="140"/>
+      <c r="J23" s="140"/>
+      <c r="K23" s="140"/>
+      <c r="L23" s="140"/>
+      <c r="M23" s="140"/>
+    </row>
+    <row r="24" spans="1:13" s="142" customFormat="1">
+      <c r="A24" s="139" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B24" s="139"/>
+      <c r="C24" s="139" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D24" s="139"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="140"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="140"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="140"/>
+    </row>
+    <row r="25" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A25" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B25" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C25" s="139" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D25" s="139"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="135" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H25" s="140"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="149" t="s">
+        <v>1543</v>
+      </c>
+      <c r="K25" s="140"/>
+      <c r="L25" s="140"/>
+      <c r="M25" s="140"/>
+    </row>
+    <row r="26" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A26" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B26" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C26" s="139" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D26" s="139"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="135" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H26" s="134" t="s">
+        <v>1544</v>
+      </c>
+      <c r="I26" s="134" t="s">
+        <v>1545</v>
+      </c>
+      <c r="J26" s="134" t="s">
+        <v>1546</v>
+      </c>
+      <c r="K26" s="140"/>
+      <c r="L26" s="140"/>
+      <c r="M26" s="140"/>
+    </row>
+    <row r="27" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A27" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B27" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C27" s="139" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D27" s="139"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="135" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H27" s="149" t="s">
+        <v>1547</v>
+      </c>
+      <c r="I27" s="134" t="s">
+        <v>1548</v>
+      </c>
+      <c r="J27" s="149" t="s">
+        <v>1548</v>
+      </c>
+      <c r="K27" s="140"/>
+      <c r="L27" s="140"/>
+      <c r="M27" s="140"/>
+    </row>
+    <row r="28" spans="1:13" s="142" customFormat="1">
+      <c r="A28" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B28" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C28" s="139" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D28" s="139"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="135" t="s">
+        <v>1443</v>
+      </c>
+      <c r="H28" s="147"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="147"/>
+      <c r="K28" s="140"/>
+      <c r="L28" s="140"/>
+      <c r="M28" s="140"/>
+    </row>
+    <row r="29" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A29" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B29" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C29" s="139" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D29" s="139"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="135" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H29" s="149" t="s">
+        <v>1549</v>
+      </c>
+      <c r="I29" s="149" t="s">
+        <v>1550</v>
+      </c>
+      <c r="J29" s="149" t="s">
+        <v>1551</v>
+      </c>
+      <c r="K29" s="140"/>
+      <c r="L29" s="140"/>
+      <c r="M29" s="140"/>
+    </row>
+    <row r="30" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A30" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B30" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C30" s="139" t="s">
+        <v>1446</v>
+      </c>
+      <c r="D30" s="139"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="135" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H30" s="149" t="s">
+        <v>1552</v>
+      </c>
+      <c r="I30" s="134" t="s">
+        <v>1553</v>
+      </c>
+      <c r="J30" s="149" t="s">
+        <v>1554</v>
+      </c>
+      <c r="K30" s="140"/>
+      <c r="L30" s="140"/>
+      <c r="M30" s="140"/>
+    </row>
+    <row r="31" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A31" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B31" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C31" s="139" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D31" s="139"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="135" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H31" s="149" t="s">
+        <v>1555</v>
+      </c>
+      <c r="I31" s="149" t="s">
+        <v>1556</v>
+      </c>
+      <c r="J31" s="149" t="s">
+        <v>1557</v>
+      </c>
+      <c r="K31" s="140"/>
+      <c r="L31" s="140"/>
+      <c r="M31" s="140"/>
+    </row>
+    <row r="32" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A32" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B32" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C32" s="139" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D32" s="139"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="135" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H32" s="149" t="s">
+        <v>1558</v>
+      </c>
+      <c r="I32" s="134" t="s">
+        <v>1453</v>
+      </c>
+      <c r="J32" s="149" t="s">
+        <v>1559</v>
+      </c>
+      <c r="K32" s="140"/>
+      <c r="L32" s="140"/>
+      <c r="M32" s="140"/>
+    </row>
+    <row r="33" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A33" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B33" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C33" s="139" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D33" s="139"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="135" t="s">
+        <v>1561</v>
+      </c>
+      <c r="H33" s="149" t="s">
+        <v>1562</v>
+      </c>
+      <c r="I33" s="149" t="s">
+        <v>1563</v>
+      </c>
+      <c r="J33" s="149" t="s">
+        <v>1564</v>
+      </c>
+      <c r="K33" s="140"/>
+      <c r="L33" s="140"/>
+      <c r="M33" s="140"/>
+    </row>
+    <row r="34" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A34" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B34" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C34" s="139" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D34" s="139"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="141"/>
+      <c r="G34" s="135" t="s">
+        <v>1566</v>
+      </c>
+      <c r="H34" s="149" t="s">
+        <v>1567</v>
+      </c>
+      <c r="I34" s="149" t="s">
+        <v>1568</v>
+      </c>
+      <c r="J34" s="149" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K34" s="140"/>
+      <c r="L34" s="140"/>
+      <c r="M34" s="140"/>
+    </row>
+    <row r="35" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A35" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B35" s="139" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C35" s="139" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D35" s="139"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="141"/>
+      <c r="G35" s="135" t="s">
+        <v>1571</v>
+      </c>
+      <c r="H35" s="149" t="s">
+        <v>1572</v>
+      </c>
+      <c r="I35" s="149" t="s">
+        <v>1573</v>
+      </c>
+      <c r="J35" s="149" t="s">
+        <v>1574</v>
+      </c>
+      <c r="K35" s="140"/>
+      <c r="L35" s="140"/>
+      <c r="M35" s="140"/>
+    </row>
+    <row r="36" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A36" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B36" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C36" s="147" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D36" s="147" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E36" s="140"/>
+      <c r="F36" s="141"/>
+      <c r="G36" s="135" t="s">
+        <v>1577</v>
+      </c>
+      <c r="H36" s="149" t="s">
+        <v>1578</v>
+      </c>
+      <c r="I36" s="149" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J36" s="149" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K36" s="140"/>
+      <c r="L36" s="140"/>
+      <c r="M36" s="140"/>
+    </row>
+    <row r="37" spans="1:13" s="142" customFormat="1">
+      <c r="A37" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B37" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C37" s="148" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D37" s="147" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E37" s="140"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="135" t="s">
+        <v>1582</v>
+      </c>
+      <c r="H37" s="140"/>
+      <c r="I37" s="140"/>
+      <c r="J37" s="140"/>
+      <c r="K37" s="140"/>
+      <c r="L37" s="140"/>
+      <c r="M37" s="140"/>
+    </row>
+    <row r="38" spans="1:13" s="142" customFormat="1">
+      <c r="A38" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B38" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C38" s="148" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D38" s="147" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E38" s="140"/>
+      <c r="F38" s="141"/>
+      <c r="G38" s="135" t="s">
+        <v>1585</v>
+      </c>
+      <c r="H38" s="140"/>
+      <c r="I38" s="140"/>
+      <c r="J38" s="140"/>
+      <c r="K38" s="140"/>
+      <c r="L38" s="140"/>
+      <c r="M38" s="140"/>
+    </row>
+    <row r="39" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A39" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B39" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C39" s="148" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D39" s="147" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E39" s="140"/>
+      <c r="F39" s="141"/>
+      <c r="G39" s="135" t="s">
+        <v>1587</v>
+      </c>
+      <c r="H39" s="149" t="s">
+        <v>1588</v>
+      </c>
+      <c r="I39" s="149" t="s">
+        <v>1589</v>
+      </c>
+      <c r="J39" s="149" t="s">
+        <v>1590</v>
+      </c>
+      <c r="K39" s="140"/>
+      <c r="L39" s="140"/>
+      <c r="M39" s="140"/>
+    </row>
+    <row r="40" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A40" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B40" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C40" s="148" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="147" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E40" s="140"/>
+      <c r="F40" s="141"/>
+      <c r="G40" s="135" t="s">
+        <v>1592</v>
+      </c>
+      <c r="H40" s="149" t="s">
+        <v>1593</v>
+      </c>
+      <c r="I40" s="140"/>
+      <c r="J40" s="149" t="s">
+        <v>1594</v>
+      </c>
+      <c r="K40" s="140"/>
+      <c r="L40" s="140"/>
+      <c r="M40" s="140"/>
+    </row>
+    <row r="41" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A41" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B41" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C41" s="148" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D41" s="147" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E41" s="140"/>
+      <c r="F41" s="141"/>
+      <c r="G41" s="135" t="s">
+        <v>1596</v>
+      </c>
+      <c r="H41" s="149" t="s">
+        <v>1597</v>
+      </c>
+      <c r="I41" s="149" t="s">
+        <v>1598</v>
+      </c>
+      <c r="J41" s="149" t="s">
+        <v>1599</v>
+      </c>
+      <c r="K41" s="140"/>
+      <c r="L41" s="140"/>
+      <c r="M41" s="140"/>
+    </row>
+    <row r="42" spans="1:13" s="142" customFormat="1">
+      <c r="A42" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B42" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C42" s="148" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D42" s="147"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="135"/>
+      <c r="H42" s="140"/>
+      <c r="I42" s="140"/>
+      <c r="J42" s="140"/>
+      <c r="K42" s="140"/>
+      <c r="L42" s="140"/>
+      <c r="M42" s="140"/>
+    </row>
+    <row r="43" spans="1:13" s="142" customFormat="1">
+      <c r="A43" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B43" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C43" s="148" t="s">
+        <v>601</v>
+      </c>
+      <c r="D43" s="147"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="135"/>
+      <c r="H43" s="140"/>
+      <c r="I43" s="140"/>
+      <c r="J43" s="140"/>
+      <c r="K43" s="140"/>
+      <c r="L43" s="140"/>
+      <c r="M43" s="140"/>
+    </row>
+    <row r="44" spans="1:13" s="142" customFormat="1">
+      <c r="A44" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B44" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C44" s="148" t="s">
+        <v>1462</v>
+      </c>
+      <c r="D44" s="147"/>
+      <c r="E44" s="140"/>
+      <c r="F44" s="141"/>
+      <c r="G44" s="135"/>
+      <c r="H44" s="140"/>
+      <c r="I44" s="140"/>
+      <c r="J44" s="140"/>
+      <c r="K44" s="140"/>
+      <c r="L44" s="140"/>
+      <c r="M44" s="140"/>
+    </row>
+    <row r="45" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A45" s="139" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B45" s="139" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C45" s="148" t="s">
+        <v>472</v>
+      </c>
+      <c r="D45" s="147"/>
+      <c r="E45" s="140"/>
+      <c r="F45" s="141"/>
+      <c r="G45" s="134" t="s">
+        <v>1600</v>
+      </c>
+      <c r="H45" s="149" t="s">
+        <v>1601</v>
+      </c>
+      <c r="I45" s="149" t="s">
+        <v>1602</v>
+      </c>
+      <c r="J45" s="149" t="s">
+        <v>1603</v>
+      </c>
+      <c r="K45" s="140"/>
+      <c r="L45" s="140"/>
+      <c r="M45" s="140"/>
+    </row>
+    <row r="46" spans="1:13" s="142" customFormat="1">
+      <c r="A46" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B46" s="139" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C46" s="139" t="s">
+        <v>1606</v>
+      </c>
+      <c r="D46" s="139" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E46" s="140"/>
+      <c r="F46" s="141"/>
+      <c r="G46" s="135" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H46" s="140"/>
+      <c r="I46" s="140"/>
+      <c r="J46" s="140"/>
+      <c r="K46" s="140"/>
+      <c r="L46" s="140"/>
+      <c r="M46" s="140"/>
+    </row>
+    <row r="47" spans="1:13" s="142" customFormat="1">
+      <c r="A47" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B47" s="139" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C47" s="139" t="s">
+        <v>1609</v>
+      </c>
+      <c r="D47" s="139" t="s">
+        <v>1610</v>
+      </c>
+      <c r="E47" s="140"/>
+      <c r="F47" s="141"/>
+      <c r="G47" s="135" t="s">
+        <v>1611</v>
+      </c>
+      <c r="H47" s="140"/>
+      <c r="I47" s="140"/>
+      <c r="J47" s="140"/>
+      <c r="K47" s="140"/>
+      <c r="L47" s="140"/>
+      <c r="M47" s="140"/>
+    </row>
+    <row r="48" spans="1:13" s="142" customFormat="1">
+      <c r="A48" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B48" s="139" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C48" s="139" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D48" s="139" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E48" s="140"/>
+      <c r="F48" s="141"/>
+      <c r="G48" s="135" t="s">
+        <v>1614</v>
+      </c>
+      <c r="H48" s="140"/>
+      <c r="I48" s="140"/>
+      <c r="J48" s="140"/>
+      <c r="K48" s="140"/>
+      <c r="L48" s="140"/>
+      <c r="M48" s="140"/>
+    </row>
+    <row r="49" spans="1:13" s="142" customFormat="1">
+      <c r="A49" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B49" s="139" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C49" s="139" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D49" s="139" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E49" s="140"/>
+      <c r="F49" s="141"/>
+      <c r="G49" s="135" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H49" s="140"/>
+      <c r="I49" s="140"/>
+      <c r="J49" s="140"/>
+      <c r="K49" s="140"/>
+      <c r="L49" s="140"/>
+      <c r="M49" s="140"/>
+    </row>
+    <row r="50" spans="1:13" s="142" customFormat="1" ht="15">
+      <c r="A50" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B50" s="139" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C50" s="139" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D50" s="139" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E50" s="140"/>
+      <c r="F50" s="141"/>
+      <c r="G50" s="149" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H50" s="140"/>
+      <c r="I50" s="140"/>
+      <c r="J50" s="140"/>
+      <c r="K50" s="140"/>
+      <c r="L50" s="140"/>
+      <c r="M50" s="140"/>
+    </row>
+    <row r="51" spans="1:13" s="142" customFormat="1">
+      <c r="A51" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B51" s="139" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C51" s="139" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D51" s="139"/>
+      <c r="E51" s="140" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F51" s="141"/>
+      <c r="G51" s="140"/>
+      <c r="H51" s="140"/>
+      <c r="I51" s="140"/>
+      <c r="J51" s="140"/>
+      <c r="K51" s="140"/>
+      <c r="L51" s="140"/>
+      <c r="M51" s="140"/>
+    </row>
+    <row r="52" spans="1:13" s="142" customFormat="1">
+      <c r="A52" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B52" s="140" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C52" s="140" t="s">
+        <v>1625</v>
+      </c>
+      <c r="D52" s="140"/>
+      <c r="E52" s="140" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F52" s="141">
+        <v>2022</v>
+      </c>
+      <c r="G52" s="135" t="s">
+        <v>1627</v>
+      </c>
+      <c r="H52" s="140"/>
+      <c r="I52" s="140"/>
+      <c r="J52" s="140"/>
+      <c r="K52" s="140"/>
+      <c r="L52" s="140"/>
+      <c r="M52" s="140"/>
+    </row>
+    <row r="53" spans="1:13" s="142" customFormat="1">
+      <c r="A53" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B53" s="140" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C53" s="140" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D53" s="140"/>
+      <c r="E53" s="140" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F53" s="141">
+        <v>2022</v>
+      </c>
+      <c r="G53" s="135" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H53" s="140"/>
+      <c r="I53" s="140"/>
+      <c r="J53" s="140"/>
+      <c r="K53" s="140"/>
+      <c r="L53" s="140"/>
+      <c r="M53" s="140"/>
+    </row>
+    <row r="54" spans="1:13" s="142" customFormat="1">
+      <c r="A54" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B54" s="140" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C54" s="140" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D54" s="140"/>
+      <c r="E54" s="140" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F54" s="141">
+        <v>2022</v>
+      </c>
+      <c r="G54" s="135" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H54" s="140"/>
+      <c r="I54" s="140"/>
+      <c r="J54" s="140"/>
+      <c r="K54" s="140"/>
+      <c r="L54" s="140"/>
+      <c r="M54" s="140"/>
+    </row>
+    <row r="55" spans="1:13" s="142" customFormat="1">
+      <c r="A55" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B55" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C55" s="140" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D55" s="140"/>
+      <c r="E55" s="140" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F55" s="141">
+        <v>2021</v>
+      </c>
+      <c r="G55" s="135" t="s">
+        <v>1636</v>
+      </c>
+      <c r="H55" s="140"/>
+      <c r="I55" s="140"/>
+      <c r="J55" s="140"/>
+      <c r="K55" s="140"/>
+      <c r="L55" s="140"/>
+      <c r="M55" s="140"/>
+    </row>
+    <row r="56" spans="1:13" s="142" customFormat="1">
+      <c r="A56" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B56" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C56" s="140" t="s">
+        <v>1637</v>
+      </c>
+      <c r="D56" s="140"/>
+      <c r="E56" s="140" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F56" s="141">
+        <v>2021</v>
+      </c>
+      <c r="G56" s="135" t="s">
         <v>1638</v>
       </c>
-      <c r="B1" s="138" t="s">
-        <v>1465</v>
-      </c>
-      <c r="C1" s="138" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D1" s="138" t="s">
+      <c r="H56" s="140"/>
+      <c r="I56" s="140"/>
+      <c r="J56" s="140"/>
+      <c r="K56" s="140"/>
+      <c r="L56" s="140"/>
+      <c r="M56" s="140"/>
+    </row>
+    <row r="57" spans="1:13" s="142" customFormat="1">
+      <c r="A57" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B57" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C57" s="140" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D57" s="140"/>
+      <c r="E57" s="140" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F57" s="141">
+        <v>2021</v>
+      </c>
+      <c r="G57" s="135" t="s">
+        <v>1640</v>
+      </c>
+      <c r="H57" s="140"/>
+      <c r="I57" s="140"/>
+      <c r="J57" s="140"/>
+      <c r="K57" s="140"/>
+      <c r="L57" s="140"/>
+      <c r="M57" s="140"/>
+    </row>
+    <row r="58" spans="1:13" s="142" customFormat="1">
+      <c r="A58" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B58" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C58" s="140" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D58" s="140"/>
+      <c r="E58" s="140" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F58" s="141">
+        <v>2021</v>
+      </c>
+      <c r="G58" s="135" t="s">
+        <v>1643</v>
+      </c>
+      <c r="H58" s="140"/>
+      <c r="I58" s="140"/>
+      <c r="J58" s="140"/>
+      <c r="K58" s="140"/>
+      <c r="L58" s="140"/>
+      <c r="M58" s="140"/>
+    </row>
+    <row r="59" spans="1:13" s="142" customFormat="1">
+      <c r="A59" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B59" s="143" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C59" s="143" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D59" s="143"/>
+      <c r="E59" s="143" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F59" s="144"/>
+      <c r="G59" s="135"/>
+      <c r="H59" s="140"/>
+      <c r="I59" s="140"/>
+      <c r="J59" s="140"/>
+      <c r="K59" s="140"/>
+      <c r="L59" s="140"/>
+      <c r="M59" s="140"/>
+    </row>
+    <row r="60" spans="1:13" s="142" customFormat="1">
+      <c r="A60" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B60" s="143" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C60" s="143" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D60" s="143"/>
+      <c r="E60" s="143" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F60" s="144"/>
+      <c r="G60" s="134" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H60" s="140"/>
+      <c r="I60" s="140"/>
+      <c r="J60" s="140"/>
+      <c r="K60" s="140"/>
+      <c r="L60" s="140"/>
+      <c r="M60" s="140"/>
+    </row>
+    <row r="61" spans="1:13" s="142" customFormat="1">
+      <c r="A61" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B61" s="143" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C61" s="143" t="s">
+        <v>1647</v>
+      </c>
+      <c r="D61" s="143"/>
+      <c r="E61" s="143" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F61" s="144"/>
+      <c r="G61" s="134" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H61" s="140"/>
+      <c r="I61" s="140"/>
+      <c r="J61" s="140"/>
+      <c r="K61" s="140"/>
+      <c r="L61" s="140"/>
+      <c r="M61" s="140"/>
+    </row>
+    <row r="62" spans="1:13" s="142" customFormat="1">
+      <c r="A62" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B62" s="143" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C62" s="143" t="s">
+        <v>1649</v>
+      </c>
+      <c r="D62" s="143"/>
+      <c r="E62" s="143" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F62" s="144"/>
+      <c r="G62" s="134" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H62" s="140"/>
+      <c r="I62" s="140"/>
+      <c r="J62" s="140"/>
+      <c r="K62" s="140"/>
+      <c r="L62" s="140"/>
+      <c r="M62" s="140"/>
+    </row>
+    <row r="63" spans="1:13" s="146" customFormat="1" ht="15.6">
+      <c r="A63" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B63" s="143" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C63" s="143" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D63" s="143"/>
+      <c r="E63" s="143" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F63" s="144"/>
+      <c r="G63" s="135" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H63" s="145"/>
+      <c r="I63" s="145"/>
+      <c r="J63" s="145"/>
+      <c r="K63" s="145"/>
+      <c r="L63" s="145"/>
+      <c r="M63" s="145"/>
+    </row>
+    <row r="64" spans="1:13" s="146" customFormat="1" ht="15.6">
+      <c r="A64" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B64" s="143" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C64" s="143" t="s">
+        <v>1653</v>
+      </c>
+      <c r="D64" s="143"/>
+      <c r="E64" s="143" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F64" s="144"/>
+      <c r="G64" s="135" t="s">
+        <v>1654</v>
+      </c>
+      <c r="H64" s="145"/>
+      <c r="I64" s="145"/>
+      <c r="J64" s="145"/>
+      <c r="K64" s="145"/>
+      <c r="L64" s="145"/>
+      <c r="M64" s="145"/>
+    </row>
+    <row r="65" spans="1:13" s="142" customFormat="1">
+      <c r="A65" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B65" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C65" s="140" t="s">
+        <v>1655</v>
+      </c>
+      <c r="D65" s="140"/>
+      <c r="E65" s="140" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F65" s="141">
+        <v>2024</v>
+      </c>
+      <c r="G65" s="135" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H65" s="140"/>
+      <c r="I65" s="140"/>
+      <c r="J65" s="140"/>
+      <c r="K65" s="140"/>
+      <c r="L65" s="140"/>
+      <c r="M65" s="140"/>
+    </row>
+    <row r="66" spans="1:13" s="142" customFormat="1">
+      <c r="A66" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B66" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C66" s="140" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D66" s="140"/>
+      <c r="E66" s="140" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F66" s="141">
+        <v>2024</v>
+      </c>
+      <c r="G66" s="135" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H66" s="140"/>
+      <c r="I66" s="140"/>
+      <c r="J66" s="140"/>
+      <c r="K66" s="140"/>
+      <c r="L66" s="140"/>
+      <c r="M66" s="140"/>
+    </row>
+    <row r="67" spans="1:13" s="142" customFormat="1">
+      <c r="A67" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B67" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C67" s="140" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D67" s="140"/>
+      <c r="E67" s="140" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F67" s="141">
+        <v>2024</v>
+      </c>
+      <c r="G67" s="135" t="s">
+        <v>1660</v>
+      </c>
+      <c r="H67" s="140"/>
+      <c r="I67" s="140"/>
+      <c r="J67" s="140"/>
+      <c r="K67" s="140"/>
+      <c r="L67" s="140"/>
+      <c r="M67" s="140"/>
+    </row>
+    <row r="68" spans="1:13" s="142" customFormat="1">
+      <c r="A68" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B68" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C68" s="140" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D68" s="140"/>
+      <c r="E68" s="140" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F68" s="141">
+        <v>2024</v>
+      </c>
+      <c r="G68" s="135" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H68" s="140"/>
+      <c r="I68" s="140"/>
+      <c r="J68" s="140"/>
+      <c r="K68" s="140"/>
+      <c r="L68" s="140"/>
+      <c r="M68" s="140"/>
+    </row>
+    <row r="69" spans="1:13" s="142" customFormat="1">
+      <c r="A69" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B69" s="140" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C69" s="140" t="s">
+        <v>1663</v>
+      </c>
+      <c r="D69" s="140"/>
+      <c r="E69" s="140" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F69" s="141">
+        <v>2023</v>
+      </c>
+      <c r="G69" s="135" t="s">
+        <v>1664</v>
+      </c>
+      <c r="H69" s="140"/>
+      <c r="I69" s="140"/>
+      <c r="J69" s="140"/>
+      <c r="K69" s="140"/>
+      <c r="L69" s="140"/>
+      <c r="M69" s="140"/>
+    </row>
+    <row r="70" spans="1:13" s="146" customFormat="1" ht="15.6">
+      <c r="A70" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B70" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C70" s="140" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D70" s="140"/>
+      <c r="E70" s="140"/>
+      <c r="F70" s="141"/>
+      <c r="G70" s="134" t="s">
+        <v>1666</v>
+      </c>
+      <c r="H70" s="134" t="s">
+        <v>1667</v>
+      </c>
+      <c r="I70" s="134" t="s">
         <v>1668</v>
       </c>
-      <c r="E1" s="138" t="s">
-        <v>1467</v>
-      </c>
-      <c r="F1" s="138" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="138" t="s">
-        <v>1468</v>
-      </c>
-      <c r="H1" s="138" t="s">
-        <v>1469</v>
-      </c>
-      <c r="I1" s="138" t="s">
-        <v>1470</v>
-      </c>
-      <c r="J1" s="138" t="s">
-        <v>1471</v>
-      </c>
-      <c r="K1" s="138" t="s">
-        <v>1472</v>
-      </c>
-      <c r="L1" s="138" t="s">
-        <v>1473</v>
-      </c>
-      <c r="M1" s="138" t="s">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="139" customFormat="1" ht="13">
-      <c r="A2" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B2" s="141" t="s">
-        <v>1649</v>
-      </c>
-      <c r="C2" s="141" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="136" t="s">
-        <v>1300</v>
-      </c>
-      <c r="H2" s="136" t="s">
-        <v>1637</v>
-      </c>
-      <c r="I2" s="136" t="s">
-        <v>1301</v>
-      </c>
-      <c r="J2" s="135"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="136"/>
-    </row>
-    <row r="3" spans="1:13" s="139" customFormat="1" ht="13">
-      <c r="A3" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B3" s="141" t="s">
-        <v>1649</v>
-      </c>
-      <c r="C3" s="141" t="s">
-        <v>1646</v>
-      </c>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="136" t="s">
-        <v>1475</v>
-      </c>
-      <c r="H3" s="135" t="s">
-        <v>1476</v>
-      </c>
-      <c r="I3" s="135" t="s">
-        <v>1228</v>
-      </c>
-      <c r="J3" s="135" t="s">
-        <v>1477</v>
-      </c>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-    </row>
-    <row r="4" spans="1:13" s="143" customFormat="1">
-      <c r="A4" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B4" s="141" t="s">
-        <v>1649</v>
-      </c>
-      <c r="C4" s="141" t="s">
-        <v>1647</v>
-      </c>
-      <c r="D4" s="141"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="135" t="s">
-        <v>1233</v>
-      </c>
-      <c r="H4" s="135" t="s">
-        <v>1235</v>
-      </c>
-      <c r="I4" s="135" t="s">
-        <v>1234</v>
-      </c>
-      <c r="J4" s="135" t="s">
-        <v>1236</v>
-      </c>
-      <c r="K4" s="141"/>
-      <c r="L4" s="141"/>
-      <c r="M4" s="141"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B5" s="141" t="s">
-        <v>1649</v>
-      </c>
-      <c r="C5" s="141" t="s">
-        <v>1537</v>
-      </c>
-      <c r="D5" s="141"/>
-      <c r="E5" s="141"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="135" t="s">
-        <v>1633</v>
-      </c>
-      <c r="H5" s="135" t="s">
-        <v>1634</v>
-      </c>
-      <c r="I5" s="135" t="s">
-        <v>1635</v>
-      </c>
-      <c r="J5" s="135" t="s">
-        <v>1636</v>
-      </c>
-      <c r="K5" s="135"/>
-      <c r="L5" s="135"/>
-      <c r="M5" s="135"/>
-    </row>
-    <row r="6" spans="1:13" s="143" customFormat="1">
-      <c r="A6" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B6" s="141"/>
-      <c r="C6" s="141" t="s">
-        <v>1478</v>
-      </c>
-      <c r="D6" s="141"/>
-      <c r="E6" s="141"/>
-      <c r="F6" s="142"/>
-      <c r="G6" s="136" t="s">
-        <v>1479</v>
-      </c>
-      <c r="H6" s="136" t="s">
-        <v>1480</v>
-      </c>
-      <c r="I6" s="136" t="s">
-        <v>1481</v>
-      </c>
-      <c r="J6" s="136" t="s">
-        <v>1482</v>
-      </c>
-      <c r="K6" s="141"/>
-      <c r="L6" s="141"/>
-      <c r="M6" s="141"/>
-    </row>
-    <row r="7" spans="1:13" s="143" customFormat="1">
-      <c r="A7" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B7" s="141"/>
-      <c r="C7" s="141" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="135" t="s">
-        <v>1484</v>
-      </c>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="141"/>
-      <c r="M7" s="141"/>
-    </row>
-    <row r="8" spans="1:13" s="143" customFormat="1">
-      <c r="A8" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B8" s="141"/>
-      <c r="C8" s="141" t="s">
-        <v>1485</v>
-      </c>
-      <c r="D8" s="141"/>
-      <c r="E8" s="141"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="135" t="s">
-        <v>1486</v>
-      </c>
-      <c r="H8" s="141"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="141"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="141"/>
-      <c r="M8" s="141"/>
-    </row>
-    <row r="9" spans="1:13" s="143" customFormat="1">
-      <c r="A9" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B9" s="141"/>
-      <c r="C9" s="141" t="s">
-        <v>1487</v>
-      </c>
-      <c r="D9" s="141"/>
-      <c r="E9" s="141"/>
-      <c r="F9" s="142"/>
-      <c r="G9" s="136" t="s">
-        <v>1488</v>
-      </c>
-      <c r="H9" s="136" t="s">
-        <v>1489</v>
-      </c>
-      <c r="I9" s="136" t="s">
-        <v>1490</v>
-      </c>
-      <c r="J9" s="136" t="s">
-        <v>1491</v>
-      </c>
-      <c r="K9" s="141"/>
-      <c r="L9" s="141"/>
-      <c r="M9" s="141"/>
-    </row>
-    <row r="10" spans="1:13" s="143" customFormat="1">
-      <c r="A10" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B10" s="141" t="s">
-        <v>1492</v>
-      </c>
-      <c r="C10" s="141" t="s">
-        <v>1493</v>
-      </c>
-      <c r="D10" s="141"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="142"/>
-      <c r="G10" s="135" t="s">
-        <v>1448</v>
-      </c>
-      <c r="H10" s="136" t="s">
-        <v>1494</v>
-      </c>
-      <c r="I10" s="136" t="s">
-        <v>1495</v>
-      </c>
-      <c r="J10" s="136" t="s">
-        <v>1496</v>
-      </c>
-      <c r="K10" s="141"/>
-      <c r="L10" s="141"/>
-      <c r="M10" s="141"/>
-    </row>
-    <row r="11" spans="1:13" s="143" customFormat="1">
-      <c r="A11" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B11" s="141" t="s">
-        <v>1492</v>
-      </c>
-      <c r="C11" s="141" t="s">
-        <v>1497</v>
-      </c>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="135" t="s">
-        <v>1498</v>
-      </c>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-    </row>
-    <row r="12" spans="1:13" s="143" customFormat="1">
-      <c r="A12" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B12" s="141" t="s">
-        <v>1492</v>
-      </c>
-      <c r="C12" s="141" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="142"/>
-      <c r="G12" s="135" t="s">
-        <v>1500</v>
-      </c>
-      <c r="H12" s="135" t="s">
-        <v>1229</v>
-      </c>
-      <c r="I12" s="135" t="s">
-        <v>1501</v>
-      </c>
-      <c r="J12" s="135" t="s">
-        <v>1230</v>
-      </c>
-      <c r="K12" s="135" t="s">
-        <v>1231</v>
-      </c>
-      <c r="L12" s="141"/>
-      <c r="M12" s="141"/>
-    </row>
-    <row r="13" spans="1:13" s="143" customFormat="1">
-      <c r="A13" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B13" s="141" t="s">
-        <v>1492</v>
-      </c>
-      <c r="C13" s="141" t="s">
-        <v>1502</v>
-      </c>
-      <c r="D13" s="141"/>
-      <c r="E13" s="141"/>
-      <c r="F13" s="142"/>
-      <c r="G13" s="135" t="s">
-        <v>1503</v>
-      </c>
-      <c r="H13" s="136" t="s">
-        <v>1504</v>
-      </c>
-      <c r="I13" s="136" t="s">
-        <v>1505</v>
-      </c>
-      <c r="J13" s="136" t="s">
-        <v>1506</v>
-      </c>
-      <c r="K13" s="141"/>
-      <c r="L13" s="141"/>
-      <c r="M13" s="141"/>
-    </row>
-    <row r="14" spans="1:13" s="143" customFormat="1">
-      <c r="A14" s="140" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B14" s="144" t="s">
-        <v>1507</v>
-      </c>
-      <c r="C14" s="144" t="s">
-        <v>1644</v>
-      </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="141"/>
-      <c r="F14" s="142"/>
-      <c r="G14" s="135" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H14" s="141"/>
-      <c r="I14" s="141"/>
-      <c r="J14" s="141"/>
-      <c r="K14" s="141"/>
-      <c r="L14" s="141"/>
-      <c r="M14" s="141"/>
-    </row>
-    <row r="15" spans="1:13" s="143" customFormat="1">
-      <c r="A15" s="140" t="s">
-        <v>1641</v>
-      </c>
-      <c r="B15" s="144" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C15" s="144" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D15" s="144"/>
-      <c r="E15" s="141"/>
-      <c r="F15" s="142"/>
-      <c r="G15" s="136" t="s">
-        <v>1510</v>
-      </c>
-      <c r="H15" s="141"/>
-      <c r="I15" s="141"/>
-      <c r="J15" s="141"/>
-      <c r="K15" s="141"/>
-      <c r="L15" s="141"/>
-      <c r="M15" s="141"/>
-    </row>
-    <row r="16" spans="1:13" s="143" customFormat="1">
-      <c r="A16" s="140" t="s">
-        <v>1641</v>
-      </c>
-      <c r="B16" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C16" s="141" t="s">
-        <v>1511</v>
-      </c>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
-      <c r="F16" s="142"/>
-      <c r="G16" s="136" t="s">
-        <v>1512</v>
-      </c>
-      <c r="H16" s="141"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="141"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="141"/>
-      <c r="M16" s="141"/>
-    </row>
-    <row r="17" spans="1:13" s="143" customFormat="1">
-      <c r="A17" s="140" t="s">
-        <v>1641</v>
-      </c>
-      <c r="B17" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C17" s="141" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="136" t="s">
-        <v>1514</v>
-      </c>
-      <c r="H17" s="141"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="141"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="141"/>
-      <c r="M17" s="141"/>
-    </row>
-    <row r="18" spans="1:13" s="143" customFormat="1">
-      <c r="A18" s="140" t="s">
-        <v>1641</v>
-      </c>
-      <c r="B18" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C18" s="141" t="s">
-        <v>1515</v>
-      </c>
-      <c r="D18" s="141"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="136" t="s">
-        <v>1516</v>
-      </c>
-      <c r="H18" s="141"/>
-      <c r="I18" s="141"/>
-      <c r="J18" s="141"/>
-      <c r="K18" s="141"/>
-      <c r="L18" s="141"/>
-      <c r="M18" s="141"/>
-    </row>
-    <row r="19" spans="1:13" s="143" customFormat="1">
-      <c r="A19" s="140" t="s">
-        <v>1641</v>
-      </c>
-      <c r="B19" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C19" s="141" t="s">
-        <v>1517</v>
-      </c>
-      <c r="D19" s="141"/>
-      <c r="E19" s="141"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="136" t="s">
-        <v>1518</v>
-      </c>
-      <c r="H19" s="141"/>
-      <c r="I19" s="141"/>
-      <c r="J19" s="141"/>
-      <c r="K19" s="141"/>
-      <c r="L19" s="141"/>
-      <c r="M19" s="141"/>
-    </row>
-    <row r="20" spans="1:13" s="143" customFormat="1">
-      <c r="A20" s="140" t="s">
-        <v>1641</v>
-      </c>
-      <c r="B20" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C20" s="141" t="s">
-        <v>1519</v>
-      </c>
-      <c r="D20" s="141"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="142"/>
-      <c r="G20" s="136" t="s">
-        <v>1520</v>
-      </c>
-      <c r="H20" s="141"/>
-      <c r="I20" s="141"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="141"/>
-      <c r="L20" s="141"/>
-      <c r="M20" s="141"/>
-    </row>
-    <row r="21" spans="1:13" s="143" customFormat="1">
-      <c r="A21" s="140" t="s">
+      <c r="J70" s="134" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K70" s="134" t="s">
+        <v>1670</v>
+      </c>
+      <c r="L70" s="134" t="s">
+        <v>1671</v>
+      </c>
+      <c r="M70" s="140"/>
+    </row>
+    <row r="71" spans="1:13" s="146" customFormat="1" ht="15.6">
+      <c r="A71" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B71" s="140" t="s">
         <v>1521</v>
       </c>
-      <c r="B21" s="140"/>
-      <c r="C21" s="140" t="s">
-        <v>1522</v>
-      </c>
-      <c r="D21" s="140"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="142"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="141"/>
-      <c r="I21" s="141"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="141"/>
-      <c r="L21" s="141"/>
-      <c r="M21" s="141"/>
-    </row>
-    <row r="22" spans="1:13" s="143" customFormat="1">
-      <c r="A22" s="140" t="s">
+      <c r="C71" s="140" t="s">
+        <v>1672</v>
+      </c>
+      <c r="D71" s="140"/>
+      <c r="E71" s="140"/>
+      <c r="F71" s="141"/>
+      <c r="G71" s="134" t="s">
+        <v>1673</v>
+      </c>
+      <c r="H71" s="134" t="s">
+        <v>1674</v>
+      </c>
+      <c r="I71" s="134" t="s">
+        <v>1675</v>
+      </c>
+      <c r="J71" s="134" t="s">
+        <v>1676</v>
+      </c>
+      <c r="K71" s="134" t="s">
+        <v>1677</v>
+      </c>
+      <c r="L71" s="134" t="s">
+        <v>1678</v>
+      </c>
+      <c r="M71" s="134" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" s="146" customFormat="1" ht="15.6">
+      <c r="A72" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B72" s="140" t="s">
         <v>1521</v>
       </c>
-      <c r="B22" s="140"/>
-      <c r="C22" s="140" t="s">
-        <v>1523</v>
-      </c>
-      <c r="D22" s="140"/>
-      <c r="E22" s="141"/>
-      <c r="F22" s="142"/>
-      <c r="G22" s="141"/>
-      <c r="H22" s="141"/>
-      <c r="I22" s="141"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="141"/>
-      <c r="L22" s="141"/>
-      <c r="M22" s="141"/>
-    </row>
-    <row r="23" spans="1:13" s="143" customFormat="1">
-      <c r="A23" s="140" t="s">
+      <c r="C72" s="140" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D72" s="140"/>
+      <c r="E72" s="140"/>
+      <c r="F72" s="141"/>
+      <c r="G72" s="134" t="s">
+        <v>1681</v>
+      </c>
+      <c r="H72" s="134" t="s">
+        <v>1682</v>
+      </c>
+      <c r="I72" s="134" t="s">
+        <v>1683</v>
+      </c>
+      <c r="J72" s="134" t="s">
+        <v>1684</v>
+      </c>
+      <c r="K72" s="134" t="s">
+        <v>1685</v>
+      </c>
+      <c r="L72" s="134" t="s">
+        <v>1686</v>
+      </c>
+      <c r="M72" s="134"/>
+    </row>
+    <row r="73" spans="1:13" s="146" customFormat="1" ht="15.6">
+      <c r="A73" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B73" s="140" t="s">
         <v>1521</v>
       </c>
-      <c r="B23" s="140"/>
-      <c r="C23" s="140" t="s">
-        <v>1524</v>
-      </c>
-      <c r="D23" s="140"/>
-      <c r="E23" s="141"/>
-      <c r="F23" s="142"/>
-      <c r="G23" s="141"/>
-      <c r="H23" s="141"/>
-      <c r="I23" s="141"/>
-      <c r="J23" s="141"/>
-      <c r="K23" s="141"/>
-      <c r="L23" s="141"/>
-      <c r="M23" s="141"/>
-    </row>
-    <row r="24" spans="1:13" s="143" customFormat="1">
-      <c r="A24" s="140" t="s">
+      <c r="C73" s="140" t="s">
+        <v>1687</v>
+      </c>
+      <c r="D73" s="140"/>
+      <c r="E73" s="140"/>
+      <c r="F73" s="141"/>
+      <c r="G73" s="134" t="s">
+        <v>1688</v>
+      </c>
+      <c r="H73" s="134" t="s">
+        <v>1689</v>
+      </c>
+      <c r="I73" s="134" t="s">
+        <v>1690</v>
+      </c>
+      <c r="J73" s="134" t="s">
+        <v>1691</v>
+      </c>
+      <c r="K73" s="134" t="s">
+        <v>1692</v>
+      </c>
+      <c r="L73" s="134" t="s">
+        <v>1693</v>
+      </c>
+      <c r="M73" s="134"/>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B74" s="140" t="s">
         <v>1521</v>
       </c>
-      <c r="B24" s="140"/>
-      <c r="C24" s="140" t="s">
-        <v>1525</v>
-      </c>
-      <c r="D24" s="140"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="142"/>
-      <c r="G24" s="141"/>
-      <c r="H24" s="141"/>
-      <c r="I24" s="141"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="141"/>
-      <c r="L24" s="141"/>
-      <c r="M24" s="141"/>
-    </row>
-    <row r="25" spans="1:13" s="143" customFormat="1">
-      <c r="A25" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B25" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C25" s="140" t="s">
-        <v>1656</v>
-      </c>
-      <c r="D25" s="140"/>
-      <c r="E25" s="141"/>
-      <c r="F25" s="142"/>
-      <c r="G25" s="136" t="s">
-        <v>1661</v>
-      </c>
-      <c r="H25" s="141"/>
-      <c r="I25" s="141"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="141"/>
-      <c r="L25" s="141"/>
-      <c r="M25" s="141"/>
-    </row>
-    <row r="26" spans="1:13" s="143" customFormat="1">
-      <c r="A26" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B26" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C26" s="140" t="s">
-        <v>1445</v>
-      </c>
-      <c r="D26" s="140"/>
-      <c r="E26" s="141"/>
-      <c r="F26" s="142"/>
-      <c r="G26" s="136" t="s">
-        <v>1448</v>
-      </c>
-      <c r="H26" s="136"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="136"/>
-      <c r="K26" s="141"/>
-      <c r="L26" s="141"/>
-      <c r="M26" s="141"/>
-    </row>
-    <row r="27" spans="1:13" s="143" customFormat="1">
-      <c r="A27" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B27" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C27" s="140" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D27" s="140"/>
-      <c r="E27" s="141"/>
-      <c r="F27" s="142"/>
-      <c r="G27" s="136" t="s">
-        <v>1449</v>
-      </c>
-      <c r="H27" s="148"/>
-      <c r="I27" s="136" t="s">
-        <v>1450</v>
-      </c>
-      <c r="J27" s="148"/>
-      <c r="K27" s="141"/>
-      <c r="L27" s="141"/>
-      <c r="M27" s="141"/>
-    </row>
-    <row r="28" spans="1:13" s="143" customFormat="1">
-      <c r="A28" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B28" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C28" s="140" t="s">
-        <v>1434</v>
-      </c>
-      <c r="D28" s="140"/>
-      <c r="E28" s="141"/>
-      <c r="F28" s="142"/>
-      <c r="G28" s="136" t="s">
-        <v>1455</v>
-      </c>
-      <c r="H28" s="148"/>
-      <c r="I28" s="148"/>
-      <c r="J28" s="148"/>
-      <c r="K28" s="141"/>
-      <c r="L28" s="141"/>
-      <c r="M28" s="141"/>
-    </row>
-    <row r="29" spans="1:13" s="143" customFormat="1">
-      <c r="A29" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B29" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C29" s="140" t="s">
-        <v>1435</v>
-      </c>
-      <c r="D29" s="140"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="136" t="s">
-        <v>1454</v>
-      </c>
-      <c r="H29" s="148"/>
-      <c r="I29" s="148"/>
-      <c r="J29" s="148"/>
-      <c r="K29" s="141"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="141"/>
-    </row>
-    <row r="30" spans="1:13" s="143" customFormat="1">
-      <c r="A30" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B30" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C30" s="140" t="s">
-        <v>1431</v>
-      </c>
-      <c r="D30" s="140"/>
-      <c r="E30" s="141"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="136" t="s">
-        <v>1452</v>
-      </c>
-      <c r="H30" s="148"/>
-      <c r="I30" s="136" t="s">
-        <v>1451</v>
-      </c>
-      <c r="J30" s="148"/>
-      <c r="K30" s="141"/>
-      <c r="L30" s="141"/>
-      <c r="M30" s="141"/>
-    </row>
-    <row r="31" spans="1:13" s="143" customFormat="1">
-      <c r="A31" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B31" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C31" s="140" t="s">
-        <v>1432</v>
-      </c>
-      <c r="D31" s="140"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="142"/>
-      <c r="G31" s="136" t="s">
-        <v>1453</v>
-      </c>
-      <c r="H31" s="148"/>
-      <c r="I31" s="148"/>
-      <c r="J31" s="148"/>
-      <c r="K31" s="141"/>
-      <c r="L31" s="141"/>
-      <c r="M31" s="141"/>
-    </row>
-    <row r="32" spans="1:13" s="143" customFormat="1">
-      <c r="A32" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B32" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C32" s="140" t="s">
-        <v>1457</v>
-      </c>
-      <c r="D32" s="140"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="136" t="s">
-        <v>1456</v>
-      </c>
-      <c r="H32" s="148"/>
-      <c r="I32" s="136" t="s">
-        <v>1461</v>
-      </c>
-      <c r="J32" s="148"/>
-      <c r="K32" s="141"/>
-      <c r="L32" s="141"/>
-      <c r="M32" s="141"/>
-    </row>
-    <row r="33" spans="1:13" s="143" customFormat="1">
-      <c r="A33" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B33" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C33" s="140" t="s">
-        <v>1526</v>
-      </c>
-      <c r="D33" s="140"/>
-      <c r="E33" s="141"/>
-      <c r="F33" s="142"/>
-      <c r="G33" s="136" t="s">
-        <v>1652</v>
-      </c>
-      <c r="H33" s="141"/>
-      <c r="I33" s="141"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="141"/>
-      <c r="L33" s="141"/>
-      <c r="M33" s="141"/>
-    </row>
-    <row r="34" spans="1:13" s="143" customFormat="1">
-      <c r="A34" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B34" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C34" s="140" t="s">
-        <v>1651</v>
-      </c>
-      <c r="D34" s="140"/>
-      <c r="E34" s="141"/>
-      <c r="F34" s="142"/>
-      <c r="G34" s="136" t="s">
-        <v>1653</v>
-      </c>
-      <c r="H34" s="141"/>
-      <c r="I34" s="141"/>
-      <c r="J34" s="141"/>
-      <c r="K34" s="141"/>
-      <c r="L34" s="141"/>
-      <c r="M34" s="141"/>
-    </row>
-    <row r="35" spans="1:13" s="143" customFormat="1">
-      <c r="A35" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B35" s="140" t="s">
-        <v>1658</v>
-      </c>
-      <c r="C35" s="140" t="s">
-        <v>1654</v>
-      </c>
-      <c r="D35" s="140"/>
-      <c r="E35" s="141"/>
-      <c r="F35" s="142"/>
-      <c r="G35" s="136" t="s">
-        <v>1655</v>
-      </c>
-      <c r="H35" s="141"/>
-      <c r="I35" s="141"/>
-      <c r="J35" s="141"/>
-      <c r="K35" s="141"/>
-      <c r="L35" s="141"/>
-      <c r="M35" s="141"/>
-    </row>
-    <row r="36" spans="1:13" s="143" customFormat="1">
-      <c r="A36" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B36" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C36" s="148" t="s">
-        <v>1462</v>
-      </c>
-      <c r="D36" s="148" t="s">
-        <v>1660</v>
-      </c>
-      <c r="E36" s="141"/>
-      <c r="F36" s="142"/>
-      <c r="G36" s="136" t="s">
-        <v>1659</v>
-      </c>
-      <c r="H36" s="141"/>
-      <c r="I36" s="141"/>
-      <c r="J36" s="141"/>
-      <c r="K36" s="141"/>
-      <c r="L36" s="141"/>
-      <c r="M36" s="141"/>
-    </row>
-    <row r="37" spans="1:13" s="143" customFormat="1">
-      <c r="A37" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B37" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C37" s="149" t="s">
-        <v>1436</v>
-      </c>
-      <c r="D37" s="148" t="s">
-        <v>1669</v>
-      </c>
-      <c r="E37" s="141"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="136" t="s">
-        <v>1666</v>
-      </c>
-      <c r="H37" s="141"/>
-      <c r="I37" s="141"/>
-      <c r="J37" s="141"/>
-      <c r="K37" s="141"/>
-      <c r="L37" s="141"/>
-      <c r="M37" s="141"/>
-    </row>
-    <row r="38" spans="1:13" s="143" customFormat="1">
-      <c r="A38" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B38" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C38" s="149" t="s">
-        <v>1663</v>
-      </c>
-      <c r="D38" s="148" t="s">
-        <v>1670</v>
-      </c>
-      <c r="E38" s="141"/>
-      <c r="F38" s="142"/>
-      <c r="G38" s="136" t="s">
-        <v>1662</v>
-      </c>
-      <c r="H38" s="141"/>
-      <c r="I38" s="141"/>
-      <c r="J38" s="141"/>
-      <c r="K38" s="141"/>
-      <c r="L38" s="141"/>
-      <c r="M38" s="141"/>
-    </row>
-    <row r="39" spans="1:13" s="143" customFormat="1">
-      <c r="A39" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B39" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C39" s="149" t="s">
-        <v>1438</v>
-      </c>
-      <c r="D39" s="148"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="142"/>
-      <c r="G39" s="136"/>
-      <c r="H39" s="141"/>
-      <c r="I39" s="141"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="141"/>
-      <c r="L39" s="141"/>
-      <c r="M39" s="141"/>
-    </row>
-    <row r="40" spans="1:13" s="143" customFormat="1">
-      <c r="A40" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B40" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C40" s="149" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D40" s="148" t="s">
-        <v>1671</v>
-      </c>
-      <c r="E40" s="141"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="136" t="s">
-        <v>1667</v>
-      </c>
-      <c r="H40" s="141"/>
-      <c r="I40" s="141"/>
-      <c r="J40" s="141"/>
-      <c r="K40" s="141"/>
-      <c r="L40" s="141"/>
-      <c r="M40" s="141"/>
-    </row>
-    <row r="41" spans="1:13" s="143" customFormat="1">
-      <c r="A41" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B41" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C41" s="149" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41" s="148" t="s">
-        <v>1672</v>
-      </c>
-      <c r="E41" s="141"/>
-      <c r="F41" s="142"/>
-      <c r="G41" s="136" t="s">
-        <v>1664</v>
-      </c>
-      <c r="H41" s="141"/>
-      <c r="I41" s="141"/>
-      <c r="J41" s="141"/>
-      <c r="K41" s="141"/>
-      <c r="L41" s="141"/>
-      <c r="M41" s="141"/>
-    </row>
-    <row r="42" spans="1:13" s="143" customFormat="1">
-      <c r="A42" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B42" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C42" s="149" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D42" s="148" t="s">
-        <v>1673</v>
-      </c>
-      <c r="E42" s="141"/>
-      <c r="F42" s="142"/>
-      <c r="G42" s="136" t="s">
-        <v>1665</v>
-      </c>
-      <c r="H42" s="141"/>
-      <c r="I42" s="141"/>
-      <c r="J42" s="141"/>
-      <c r="K42" s="141"/>
-      <c r="L42" s="141"/>
-      <c r="M42" s="141"/>
-    </row>
-    <row r="43" spans="1:13" s="143" customFormat="1">
-      <c r="A43" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B43" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C43" s="149" t="s">
-        <v>1396</v>
-      </c>
-      <c r="D43" s="148"/>
-      <c r="E43" s="141"/>
-      <c r="F43" s="142"/>
-      <c r="G43" s="136"/>
-      <c r="H43" s="141"/>
-      <c r="I43" s="141"/>
-      <c r="J43" s="141"/>
-      <c r="K43" s="141"/>
-      <c r="L43" s="141"/>
-      <c r="M43" s="141"/>
-    </row>
-    <row r="44" spans="1:13" s="143" customFormat="1">
-      <c r="A44" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B44" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C44" s="149" t="s">
-        <v>601</v>
-      </c>
-      <c r="D44" s="148"/>
-      <c r="E44" s="141"/>
-      <c r="F44" s="142"/>
-      <c r="G44" s="136"/>
-      <c r="H44" s="141"/>
-      <c r="I44" s="141"/>
-      <c r="J44" s="141"/>
-      <c r="K44" s="141"/>
-      <c r="L44" s="141"/>
-      <c r="M44" s="141"/>
-    </row>
-    <row r="45" spans="1:13" s="143" customFormat="1">
-      <c r="A45" s="140" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B45" s="140" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C45" s="149" t="s">
-        <v>1440</v>
-      </c>
-      <c r="D45" s="148"/>
-      <c r="E45" s="141"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="136"/>
-      <c r="H45" s="141"/>
-      <c r="I45" s="141"/>
-      <c r="J45" s="141"/>
-      <c r="K45" s="141"/>
-      <c r="L45" s="141"/>
-      <c r="M45" s="141"/>
-    </row>
-    <row r="46" spans="1:13" s="143" customFormat="1">
-      <c r="A46" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B46" s="140" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C46" s="140" t="s">
-        <v>1674</v>
-      </c>
-      <c r="D46" s="140" t="s">
-        <v>1527</v>
-      </c>
-      <c r="E46" s="141"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="136" t="s">
-        <v>1528</v>
-      </c>
-      <c r="H46" s="141"/>
-      <c r="I46" s="141"/>
-      <c r="J46" s="141"/>
-      <c r="K46" s="141"/>
-      <c r="L46" s="141"/>
-      <c r="M46" s="141"/>
-    </row>
-    <row r="47" spans="1:13" s="143" customFormat="1">
-      <c r="A47" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B47" s="140" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C47" s="140" t="s">
-        <v>1529</v>
-      </c>
-      <c r="D47" s="140" t="s">
-        <v>1675</v>
-      </c>
-      <c r="E47" s="141"/>
-      <c r="F47" s="142"/>
-      <c r="G47" s="136" t="s">
-        <v>1530</v>
-      </c>
-      <c r="H47" s="141"/>
-      <c r="I47" s="141"/>
-      <c r="J47" s="141"/>
-      <c r="K47" s="141"/>
-      <c r="L47" s="141"/>
-      <c r="M47" s="141"/>
-    </row>
-    <row r="48" spans="1:13" s="143" customFormat="1">
-      <c r="A48" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B48" s="140" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C48" s="140" t="s">
-        <v>1531</v>
-      </c>
-      <c r="D48" s="140" t="s">
-        <v>1676</v>
-      </c>
-      <c r="E48" s="141"/>
-      <c r="F48" s="142"/>
-      <c r="G48" s="136" t="s">
-        <v>1532</v>
-      </c>
-      <c r="H48" s="141"/>
-      <c r="I48" s="141"/>
-      <c r="J48" s="141"/>
-      <c r="K48" s="141"/>
-      <c r="L48" s="141"/>
-      <c r="M48" s="141"/>
-    </row>
-    <row r="49" spans="1:13" s="143" customFormat="1">
-      <c r="A49" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B49" s="140" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C49" s="140" t="s">
-        <v>1533</v>
-      </c>
-      <c r="D49" s="140" t="s">
-        <v>1677</v>
-      </c>
-      <c r="E49" s="141"/>
-      <c r="F49" s="142"/>
-      <c r="G49" s="136" t="s">
-        <v>1534</v>
-      </c>
-      <c r="H49" s="141"/>
-      <c r="I49" s="141"/>
-      <c r="J49" s="141"/>
-      <c r="K49" s="141"/>
-      <c r="L49" s="141"/>
-      <c r="M49" s="141"/>
-    </row>
-    <row r="50" spans="1:13" s="143" customFormat="1">
-      <c r="A50" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B50" s="140" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C50" s="140" t="s">
-        <v>1642</v>
-      </c>
-      <c r="D50" s="140" t="s">
-        <v>1678</v>
-      </c>
-      <c r="E50" s="141"/>
-      <c r="F50" s="142"/>
-      <c r="G50" s="141"/>
-      <c r="H50" s="141"/>
-      <c r="I50" s="141"/>
-      <c r="J50" s="141"/>
-      <c r="K50" s="141"/>
-      <c r="L50" s="141"/>
-      <c r="M50" s="141"/>
-    </row>
-    <row r="51" spans="1:13" s="143" customFormat="1">
-      <c r="A51" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B51" s="140" t="s">
-        <v>1645</v>
-      </c>
-      <c r="C51" s="140" t="s">
-        <v>1535</v>
-      </c>
-      <c r="D51" s="140"/>
-      <c r="E51" s="141" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F51" s="142"/>
-      <c r="G51" s="141"/>
-      <c r="H51" s="141"/>
-      <c r="I51" s="141"/>
-      <c r="J51" s="141"/>
-      <c r="K51" s="141"/>
-      <c r="L51" s="141"/>
-      <c r="M51" s="141"/>
-    </row>
-    <row r="52" spans="1:13" s="143" customFormat="1">
-      <c r="A52" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B52" s="141" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C52" s="141" t="s">
-        <v>1539</v>
-      </c>
-      <c r="D52" s="141"/>
-      <c r="E52" s="141" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F52" s="142">
-        <v>2022</v>
-      </c>
-      <c r="G52" s="136" t="s">
-        <v>1541</v>
-      </c>
-      <c r="H52" s="141"/>
-      <c r="I52" s="141"/>
-      <c r="J52" s="141"/>
-      <c r="K52" s="141"/>
-      <c r="L52" s="141"/>
-      <c r="M52" s="141"/>
-    </row>
-    <row r="53" spans="1:13" s="143" customFormat="1">
-      <c r="A53" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B53" s="141" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C53" s="141" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D53" s="141"/>
-      <c r="E53" s="141" t="s">
-        <v>1543</v>
-      </c>
-      <c r="F53" s="142">
-        <v>2022</v>
-      </c>
-      <c r="G53" s="136" t="s">
-        <v>1544</v>
-      </c>
-      <c r="H53" s="141"/>
-      <c r="I53" s="141"/>
-      <c r="J53" s="141"/>
-      <c r="K53" s="141"/>
-      <c r="L53" s="141"/>
-      <c r="M53" s="141"/>
-    </row>
-    <row r="54" spans="1:13" s="143" customFormat="1">
-      <c r="A54" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B54" s="141" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C54" s="141" t="s">
-        <v>1545</v>
-      </c>
-      <c r="D54" s="141"/>
-      <c r="E54" s="141" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F54" s="142">
-        <v>2022</v>
-      </c>
-      <c r="G54" s="136" t="s">
-        <v>1547</v>
-      </c>
-      <c r="H54" s="141"/>
-      <c r="I54" s="141"/>
-      <c r="J54" s="141"/>
-      <c r="K54" s="141"/>
-      <c r="L54" s="141"/>
-      <c r="M54" s="141"/>
-    </row>
-    <row r="55" spans="1:13" s="143" customFormat="1">
-      <c r="A55" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B55" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C55" s="141" t="s">
-        <v>1643</v>
-      </c>
-      <c r="D55" s="141"/>
-      <c r="E55" s="141" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F55" s="142">
-        <v>2021</v>
-      </c>
-      <c r="G55" s="136" t="s">
-        <v>1549</v>
-      </c>
-      <c r="H55" s="141"/>
-      <c r="I55" s="141"/>
-      <c r="J55" s="141"/>
-      <c r="K55" s="141"/>
-      <c r="L55" s="141"/>
-      <c r="M55" s="141"/>
-    </row>
-    <row r="56" spans="1:13" s="143" customFormat="1">
-      <c r="A56" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B56" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C56" s="141" t="s">
-        <v>1550</v>
-      </c>
-      <c r="D56" s="141"/>
-      <c r="E56" s="141" t="s">
-        <v>1540</v>
-      </c>
-      <c r="F56" s="142">
-        <v>2021</v>
-      </c>
-      <c r="G56" s="136" t="s">
-        <v>1551</v>
-      </c>
-      <c r="H56" s="141"/>
-      <c r="I56" s="141"/>
-      <c r="J56" s="141"/>
-      <c r="K56" s="141"/>
-      <c r="L56" s="141"/>
-      <c r="M56" s="141"/>
-    </row>
-    <row r="57" spans="1:13" s="143" customFormat="1">
-      <c r="A57" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B57" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C57" s="141" t="s">
-        <v>1552</v>
-      </c>
-      <c r="D57" s="141"/>
-      <c r="E57" s="141" t="s">
-        <v>1543</v>
-      </c>
-      <c r="F57" s="142">
-        <v>2021</v>
-      </c>
-      <c r="G57" s="136" t="s">
-        <v>1553</v>
-      </c>
-      <c r="H57" s="141"/>
-      <c r="I57" s="141"/>
-      <c r="J57" s="141"/>
-      <c r="K57" s="141"/>
-      <c r="L57" s="141"/>
-      <c r="M57" s="141"/>
-    </row>
-    <row r="58" spans="1:13" s="143" customFormat="1">
-      <c r="A58" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B58" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C58" s="141" t="s">
-        <v>1554</v>
-      </c>
-      <c r="D58" s="141"/>
-      <c r="E58" s="141" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F58" s="142">
-        <v>2021</v>
-      </c>
-      <c r="G58" s="136" t="s">
-        <v>1556</v>
-      </c>
-      <c r="H58" s="141"/>
-      <c r="I58" s="141"/>
-      <c r="J58" s="141"/>
-      <c r="K58" s="141"/>
-      <c r="L58" s="141"/>
-      <c r="M58" s="141"/>
-    </row>
-    <row r="59" spans="1:13" s="143" customFormat="1">
-      <c r="A59" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B59" s="144" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C59" s="144" t="s">
-        <v>1557</v>
-      </c>
-      <c r="D59" s="144"/>
-      <c r="E59" s="144" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F59" s="145"/>
-      <c r="G59" s="136"/>
-      <c r="H59" s="141"/>
-      <c r="I59" s="141"/>
-      <c r="J59" s="141"/>
-      <c r="K59" s="141"/>
-      <c r="L59" s="141"/>
-      <c r="M59" s="141"/>
-    </row>
-    <row r="60" spans="1:13" s="143" customFormat="1">
-      <c r="A60" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B60" s="144" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C60" s="144" t="s">
-        <v>1558</v>
-      </c>
-      <c r="D60" s="144"/>
-      <c r="E60" s="144" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F60" s="145"/>
-      <c r="G60" s="135" t="s">
-        <v>1559</v>
-      </c>
-      <c r="H60" s="141"/>
-      <c r="I60" s="141"/>
-      <c r="J60" s="141"/>
-      <c r="K60" s="141"/>
-      <c r="L60" s="141"/>
-      <c r="M60" s="141"/>
-    </row>
-    <row r="61" spans="1:13" s="143" customFormat="1">
-      <c r="A61" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B61" s="144" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C61" s="144" t="s">
-        <v>1560</v>
-      </c>
-      <c r="D61" s="144"/>
-      <c r="E61" s="144" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F61" s="145"/>
-      <c r="G61" s="135" t="s">
-        <v>1561</v>
-      </c>
-      <c r="H61" s="141"/>
-      <c r="I61" s="141"/>
-      <c r="J61" s="141"/>
-      <c r="K61" s="141"/>
-      <c r="L61" s="141"/>
-      <c r="M61" s="141"/>
-    </row>
-    <row r="62" spans="1:13" s="143" customFormat="1">
-      <c r="A62" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B62" s="144" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C62" s="144" t="s">
-        <v>1562</v>
-      </c>
-      <c r="D62" s="144"/>
-      <c r="E62" s="144" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F62" s="145"/>
-      <c r="G62" s="135" t="s">
-        <v>1563</v>
-      </c>
-      <c r="H62" s="141"/>
-      <c r="I62" s="141"/>
-      <c r="J62" s="141"/>
-      <c r="K62" s="141"/>
-      <c r="L62" s="141"/>
-      <c r="M62" s="141"/>
-    </row>
-    <row r="63" spans="1:13" s="147" customFormat="1" ht="15.5">
-      <c r="A63" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B63" s="144" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C63" s="144" t="s">
-        <v>1564</v>
-      </c>
-      <c r="D63" s="144"/>
-      <c r="E63" s="144" t="s">
-        <v>1543</v>
-      </c>
-      <c r="F63" s="145"/>
-      <c r="G63" s="136" t="s">
-        <v>1565</v>
-      </c>
-      <c r="H63" s="146"/>
-      <c r="I63" s="146"/>
-      <c r="J63" s="146"/>
-      <c r="K63" s="146"/>
-      <c r="L63" s="146"/>
-      <c r="M63" s="146"/>
-    </row>
-    <row r="64" spans="1:13" s="147" customFormat="1" ht="15.5">
-      <c r="A64" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B64" s="144" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C64" s="144" t="s">
-        <v>1566</v>
-      </c>
-      <c r="D64" s="144"/>
-      <c r="E64" s="144" t="s">
-        <v>1543</v>
-      </c>
-      <c r="F64" s="145"/>
-      <c r="G64" s="136" t="s">
-        <v>1567</v>
-      </c>
-      <c r="H64" s="146"/>
-      <c r="I64" s="146"/>
-      <c r="J64" s="146"/>
-      <c r="K64" s="146"/>
-      <c r="L64" s="146"/>
-      <c r="M64" s="146"/>
-    </row>
-    <row r="65" spans="1:13" s="143" customFormat="1">
-      <c r="A65" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B65" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C65" s="141" t="s">
-        <v>1568</v>
-      </c>
-      <c r="D65" s="141"/>
-      <c r="E65" s="141" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F65" s="142">
-        <v>2024</v>
-      </c>
-      <c r="G65" s="136" t="s">
-        <v>1569</v>
-      </c>
-      <c r="H65" s="141"/>
-      <c r="I65" s="141"/>
-      <c r="J65" s="141"/>
-      <c r="K65" s="141"/>
-      <c r="L65" s="141"/>
-      <c r="M65" s="141"/>
-    </row>
-    <row r="66" spans="1:13" s="143" customFormat="1">
-      <c r="A66" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B66" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C66" s="141" t="s">
-        <v>1570</v>
-      </c>
-      <c r="D66" s="141"/>
-      <c r="E66" s="141" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F66" s="142">
-        <v>2024</v>
-      </c>
-      <c r="G66" s="136" t="s">
-        <v>1571</v>
-      </c>
-      <c r="H66" s="141"/>
-      <c r="I66" s="141"/>
-      <c r="J66" s="141"/>
-      <c r="K66" s="141"/>
-      <c r="L66" s="141"/>
-      <c r="M66" s="141"/>
-    </row>
-    <row r="67" spans="1:13" s="143" customFormat="1">
-      <c r="A67" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B67" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C67" s="141" t="s">
-        <v>1572</v>
-      </c>
-      <c r="D67" s="141"/>
-      <c r="E67" s="141" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F67" s="142">
-        <v>2024</v>
-      </c>
-      <c r="G67" s="136" t="s">
-        <v>1573</v>
-      </c>
-      <c r="H67" s="141"/>
-      <c r="I67" s="141"/>
-      <c r="J67" s="141"/>
-      <c r="K67" s="141"/>
-      <c r="L67" s="141"/>
-      <c r="M67" s="141"/>
-    </row>
-    <row r="68" spans="1:13" s="143" customFormat="1">
-      <c r="A68" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B68" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C68" s="141" t="s">
-        <v>1574</v>
-      </c>
-      <c r="D68" s="141"/>
-      <c r="E68" s="141" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F68" s="142">
-        <v>2024</v>
-      </c>
-      <c r="G68" s="136" t="s">
-        <v>1575</v>
-      </c>
-      <c r="H68" s="141"/>
-      <c r="I68" s="141"/>
-      <c r="J68" s="141"/>
-      <c r="K68" s="141"/>
-      <c r="L68" s="141"/>
-      <c r="M68" s="141"/>
-    </row>
-    <row r="69" spans="1:13" s="143" customFormat="1">
-      <c r="A69" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B69" s="141" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C69" s="141" t="s">
-        <v>1576</v>
-      </c>
-      <c r="D69" s="141"/>
-      <c r="E69" s="141" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F69" s="142">
-        <v>2023</v>
-      </c>
-      <c r="G69" s="136" t="s">
-        <v>1577</v>
-      </c>
-      <c r="H69" s="141"/>
-      <c r="I69" s="141"/>
-      <c r="J69" s="141"/>
-      <c r="K69" s="141"/>
-      <c r="L69" s="141"/>
-      <c r="M69" s="141"/>
-    </row>
-    <row r="70" spans="1:13" s="147" customFormat="1" ht="15.5">
-      <c r="A70" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B70" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C70" s="141" t="s">
-        <v>1463</v>
-      </c>
-      <c r="D70" s="141"/>
-      <c r="E70" s="141"/>
-      <c r="F70" s="142"/>
-      <c r="G70" s="135" t="s">
-        <v>1578</v>
-      </c>
-      <c r="H70" s="135" t="s">
-        <v>1579</v>
-      </c>
-      <c r="I70" s="135" t="s">
-        <v>1580</v>
-      </c>
-      <c r="J70" s="135" t="s">
-        <v>1581</v>
-      </c>
-      <c r="K70" s="135" t="s">
-        <v>1582</v>
-      </c>
-      <c r="L70" s="135" t="s">
-        <v>1583</v>
-      </c>
-      <c r="M70" s="141"/>
-    </row>
-    <row r="71" spans="1:13" s="147" customFormat="1" ht="15.5">
-      <c r="A71" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B71" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C71" s="141" t="s">
-        <v>1584</v>
-      </c>
-      <c r="D71" s="141"/>
-      <c r="E71" s="141"/>
-      <c r="F71" s="142"/>
-      <c r="G71" s="135" t="s">
-        <v>1585</v>
-      </c>
-      <c r="H71" s="135" t="s">
-        <v>1586</v>
-      </c>
-      <c r="I71" s="135" t="s">
-        <v>1587</v>
-      </c>
-      <c r="J71" s="135" t="s">
-        <v>1588</v>
-      </c>
-      <c r="K71" s="135" t="s">
-        <v>1589</v>
-      </c>
-      <c r="L71" s="135" t="s">
-        <v>1590</v>
-      </c>
-      <c r="M71" s="135" t="s">
-        <v>1591</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" s="147" customFormat="1" ht="15.5">
-      <c r="A72" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B72" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C72" s="141" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D72" s="141"/>
-      <c r="E72" s="141"/>
-      <c r="F72" s="142"/>
-      <c r="G72" s="135" t="s">
-        <v>1592</v>
-      </c>
-      <c r="H72" s="135" t="s">
-        <v>1593</v>
-      </c>
-      <c r="I72" s="135" t="s">
-        <v>1594</v>
-      </c>
-      <c r="J72" s="135" t="s">
-        <v>1595</v>
-      </c>
-      <c r="K72" s="135" t="s">
-        <v>1596</v>
-      </c>
-      <c r="L72" s="135" t="s">
-        <v>1597</v>
-      </c>
-      <c r="M72" s="135"/>
-    </row>
-    <row r="73" spans="1:13" s="147" customFormat="1" ht="15.5">
-      <c r="A73" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B73" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C73" s="141" t="s">
-        <v>1598</v>
-      </c>
-      <c r="D73" s="141"/>
-      <c r="E73" s="141"/>
-      <c r="F73" s="142"/>
-      <c r="G73" s="135" t="s">
-        <v>1599</v>
-      </c>
-      <c r="H73" s="135" t="s">
-        <v>1600</v>
-      </c>
-      <c r="I73" s="135" t="s">
-        <v>1601</v>
-      </c>
-      <c r="J73" s="135" t="s">
-        <v>1602</v>
-      </c>
-      <c r="K73" s="135" t="s">
-        <v>1603</v>
-      </c>
-      <c r="L73" s="135" t="s">
+      <c r="C74" s="140" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D74" s="140"/>
+      <c r="E74" s="140"/>
+      <c r="F74" s="141"/>
+      <c r="G74" s="134" t="s">
+        <v>1695</v>
+      </c>
+      <c r="H74" s="134" t="s">
+        <v>1696</v>
+      </c>
+      <c r="I74" s="134" t="s">
+        <v>1697</v>
+      </c>
+      <c r="J74" s="134" t="s">
+        <v>1698</v>
+      </c>
+      <c r="K74" s="134" t="s">
+        <v>1699</v>
+      </c>
+      <c r="L74" s="134" t="s">
+        <v>1700</v>
+      </c>
+      <c r="M74" s="134"/>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="139" t="s">
         <v>1604</v>
       </c>
-      <c r="M73" s="135"/>
-    </row>
-    <row r="74" spans="1:13">
-      <c r="A74" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B74" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C74" s="141" t="s">
-        <v>1605</v>
-      </c>
-      <c r="D74" s="141"/>
-      <c r="E74" s="141"/>
-      <c r="F74" s="142"/>
-      <c r="G74" s="135" t="s">
-        <v>1606</v>
-      </c>
-      <c r="H74" s="135" t="s">
-        <v>1607</v>
-      </c>
-      <c r="I74" s="135" t="s">
-        <v>1608</v>
-      </c>
-      <c r="J74" s="135" t="s">
-        <v>1609</v>
-      </c>
-      <c r="K74" s="135" t="s">
-        <v>1610</v>
-      </c>
-      <c r="L74" s="135" t="s">
-        <v>1611</v>
-      </c>
-      <c r="M74" s="135"/>
-    </row>
-    <row r="75" spans="1:13">
-      <c r="A75" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B75" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C75" s="141" t="s">
-        <v>1612</v>
-      </c>
-      <c r="D75" s="141"/>
-      <c r="E75" s="141"/>
-      <c r="F75" s="142"/>
-      <c r="G75" s="135" t="s">
-        <v>1613</v>
-      </c>
-      <c r="H75" s="135" t="s">
-        <v>1614</v>
-      </c>
-      <c r="I75" s="135" t="s">
-        <v>1615</v>
-      </c>
-      <c r="J75" s="135" t="s">
-        <v>1616</v>
-      </c>
-      <c r="K75" s="135" t="s">
-        <v>1617</v>
-      </c>
-      <c r="L75" s="135" t="s">
-        <v>1618</v>
-      </c>
-      <c r="M75" s="135"/>
+      <c r="B75" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C75" s="140" t="s">
+        <v>1701</v>
+      </c>
+      <c r="D75" s="140"/>
+      <c r="E75" s="140"/>
+      <c r="F75" s="141"/>
+      <c r="G75" s="134" t="s">
+        <v>1702</v>
+      </c>
+      <c r="H75" s="134" t="s">
+        <v>1703</v>
+      </c>
+      <c r="I75" s="134" t="s">
+        <v>1704</v>
+      </c>
+      <c r="J75" s="134" t="s">
+        <v>1705</v>
+      </c>
+      <c r="K75" s="134" t="s">
+        <v>1706</v>
+      </c>
+      <c r="L75" s="134" t="s">
+        <v>1707</v>
+      </c>
+      <c r="M75" s="134"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B76" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C76" s="141" t="s">
-        <v>1619</v>
-      </c>
-      <c r="D76" s="141"/>
-      <c r="E76" s="141"/>
-      <c r="F76" s="142"/>
-      <c r="G76" s="135" t="s">
-        <v>1620</v>
-      </c>
-      <c r="H76" s="135" t="s">
-        <v>1621</v>
-      </c>
-      <c r="I76" s="135" t="s">
-        <v>1622</v>
-      </c>
-      <c r="J76" s="135" t="s">
-        <v>1623</v>
-      </c>
-      <c r="K76" s="135" t="s">
-        <v>1624</v>
-      </c>
-      <c r="L76" s="135" t="s">
-        <v>1625</v>
-      </c>
-      <c r="M76" s="135"/>
+      <c r="A76" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B76" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C76" s="140" t="s">
+        <v>1708</v>
+      </c>
+      <c r="D76" s="140"/>
+      <c r="E76" s="140"/>
+      <c r="F76" s="141"/>
+      <c r="G76" s="134" t="s">
+        <v>1709</v>
+      </c>
+      <c r="H76" s="134" t="s">
+        <v>1710</v>
+      </c>
+      <c r="I76" s="134" t="s">
+        <v>1711</v>
+      </c>
+      <c r="J76" s="134" t="s">
+        <v>1712</v>
+      </c>
+      <c r="K76" s="134" t="s">
+        <v>1713</v>
+      </c>
+      <c r="L76" s="134" t="s">
+        <v>1714</v>
+      </c>
+      <c r="M76" s="134"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="140" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B77" s="141" t="s">
-        <v>1508</v>
-      </c>
-      <c r="C77" s="141" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D77" s="141"/>
-      <c r="E77" s="141"/>
-      <c r="F77" s="142"/>
-      <c r="G77" s="135" t="s">
-        <v>1627</v>
-      </c>
-      <c r="H77" s="135" t="s">
-        <v>1628</v>
-      </c>
-      <c r="I77" s="135" t="s">
-        <v>1629</v>
-      </c>
-      <c r="J77" s="135" t="s">
-        <v>1630</v>
-      </c>
-      <c r="K77" s="135" t="s">
-        <v>1631</v>
-      </c>
-      <c r="L77" s="135" t="s">
-        <v>1632</v>
-      </c>
-      <c r="M77" s="135"/>
-    </row>
+      <c r="A77" s="139" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B77" s="140" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C77" s="140" t="s">
+        <v>1715</v>
+      </c>
+      <c r="D77" s="140"/>
+      <c r="E77" s="140"/>
+      <c r="F77" s="141"/>
+      <c r="G77" s="134" t="s">
+        <v>1716</v>
+      </c>
+      <c r="H77" s="134" t="s">
+        <v>1717</v>
+      </c>
+      <c r="I77" s="134" t="s">
+        <v>1718</v>
+      </c>
+      <c r="J77" s="134" t="s">
+        <v>1719</v>
+      </c>
+      <c r="K77" s="134" t="s">
+        <v>1720</v>
+      </c>
+      <c r="L77" s="134" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M77" s="134"/>
+    </row>
+    <row r="78" spans="1:13" ht="12.75"/>
   </sheetData>
   <autoFilter ref="A1:M77" xr:uid="{5274E520-0DCC-4EC6-A7BF-2432E418040B}"/>
   <hyperlinks>
@@ -31159,56 +31366,77 @@
     <hyperlink ref="H2" r:id="rId113" xr:uid="{82ABF87B-8AA6-4A35-A152-BA451FD781EC}"/>
     <hyperlink ref="G26" r:id="rId114" xr:uid="{DD8FE194-DE9E-40F1-B5CB-F5F50372BB3A}"/>
     <hyperlink ref="G27" r:id="rId115" xr:uid="{A1319BC0-4474-47AE-952E-D2E5F8F0351E}"/>
-    <hyperlink ref="I27" r:id="rId116" xr:uid="{580DD122-F3F9-406E-B7A5-25AC17EDE181}"/>
-    <hyperlink ref="I30" r:id="rId117" xr:uid="{58244BAC-03FD-4265-9E08-595151FF5EA0}"/>
-    <hyperlink ref="G30" r:id="rId118" xr:uid="{0D3D0164-FF6C-41DA-B12B-0686EDB87DA1}"/>
-    <hyperlink ref="G31" r:id="rId119" xr:uid="{A82BD3B9-15C2-4F9E-847C-7620DE42BEA3}"/>
-    <hyperlink ref="G29" r:id="rId120" xr:uid="{A3D31B6B-7DD8-43B6-880C-B2AB37F3853F}"/>
-    <hyperlink ref="G28" r:id="rId121" xr:uid="{B7240C91-DEA5-4F40-BA5F-3AD1E3381A8A}"/>
-    <hyperlink ref="G32" r:id="rId122" xr:uid="{9D00AFD1-71CC-4BA7-9B2C-392C3AE760FD}"/>
-    <hyperlink ref="I32" r:id="rId123" xr:uid="{4AE59A7D-C30D-46D4-887D-BDB7C348B6FD}"/>
-    <hyperlink ref="G33" r:id="rId124" xr:uid="{EC6F374A-9229-43F4-8B72-C1B2B5C039E7}"/>
-    <hyperlink ref="G34" r:id="rId125" xr:uid="{D15DC9B3-E7CE-4748-A372-421CDD93C595}"/>
-    <hyperlink ref="G35" r:id="rId126" xr:uid="{8CF59088-AF3D-4195-ACC8-DB627B294094}"/>
-    <hyperlink ref="G36" r:id="rId127" xr:uid="{8F9C0119-3CD5-4D02-AB21-745AF63050F9}"/>
-    <hyperlink ref="G25" r:id="rId128" xr:uid="{865B6546-3E92-4548-9714-7AFB3308526F}"/>
-    <hyperlink ref="G38" r:id="rId129" xr:uid="{719867B3-C265-4C4B-BC29-8D956CA8CAF0}"/>
-    <hyperlink ref="G41" r:id="rId130" xr:uid="{E8DE21B5-8A7A-4737-BE0B-E64008E6446B}"/>
-    <hyperlink ref="G42" r:id="rId131" xr:uid="{330F478A-D3BE-4BB9-B9AC-A86143BA364F}"/>
-    <hyperlink ref="G37" r:id="rId132" xr:uid="{16961A32-2D19-4467-AC33-5E855F33D6F4}"/>
-    <hyperlink ref="G40" r:id="rId133" xr:uid="{02756A59-0545-4A40-8CC1-01FCFDA1877A}"/>
-    <hyperlink ref="G7" r:id="rId134" display="https://ifrcorg.sharepoint.com/sites/PERcoreworkinggroup-PERcoreworkinggroup/Shared Documents/PER core working group/PER Resources/../../../../IFRCSharing/NS%20Preparedness/Forms/AllItems.aspx?id=%2Fsites%2FIFRCSharing%2FNS%20Preparedness%2FPER%20Promotional%20pack%2FPER%20Promotional%20pack%20EN%2FPER%20in%20operations&amp;p=true&amp;ga=1" xr:uid="{3515EDD3-49BB-4408-9794-335FBE22B273}"/>
-    <hyperlink ref="G8" r:id="rId135" xr:uid="{CEF90331-72A7-4DE7-A3C8-A528F2AD1CF9}"/>
+    <hyperlink ref="I30" r:id="rId116" xr:uid="{58244BAC-03FD-4265-9E08-595151FF5EA0}"/>
+    <hyperlink ref="G30" r:id="rId117" xr:uid="{0D3D0164-FF6C-41DA-B12B-0686EDB87DA1}"/>
+    <hyperlink ref="G31" r:id="rId118" xr:uid="{A82BD3B9-15C2-4F9E-847C-7620DE42BEA3}"/>
+    <hyperlink ref="G29" r:id="rId119" xr:uid="{A3D31B6B-7DD8-43B6-880C-B2AB37F3853F}"/>
+    <hyperlink ref="G28" r:id="rId120" xr:uid="{B7240C91-DEA5-4F40-BA5F-3AD1E3381A8A}"/>
+    <hyperlink ref="G32" r:id="rId121" xr:uid="{9D00AFD1-71CC-4BA7-9B2C-392C3AE760FD}"/>
+    <hyperlink ref="I32" r:id="rId122" xr:uid="{4AE59A7D-C30D-46D4-887D-BDB7C348B6FD}"/>
+    <hyperlink ref="G33" r:id="rId123" xr:uid="{EC6F374A-9229-43F4-8B72-C1B2B5C039E7}"/>
+    <hyperlink ref="G34" r:id="rId124" xr:uid="{D15DC9B3-E7CE-4748-A372-421CDD93C595}"/>
+    <hyperlink ref="G35" r:id="rId125" xr:uid="{8CF59088-AF3D-4195-ACC8-DB627B294094}"/>
+    <hyperlink ref="G36" r:id="rId126" xr:uid="{8F9C0119-3CD5-4D02-AB21-745AF63050F9}"/>
+    <hyperlink ref="G25" r:id="rId127" xr:uid="{865B6546-3E92-4548-9714-7AFB3308526F}"/>
+    <hyperlink ref="G38" r:id="rId128" xr:uid="{719867B3-C265-4C4B-BC29-8D956CA8CAF0}"/>
+    <hyperlink ref="G40" r:id="rId129" xr:uid="{E8DE21B5-8A7A-4737-BE0B-E64008E6446B}"/>
+    <hyperlink ref="G41" r:id="rId130" xr:uid="{330F478A-D3BE-4BB9-B9AC-A86143BA364F}"/>
+    <hyperlink ref="G37" r:id="rId131" xr:uid="{16961A32-2D19-4467-AC33-5E855F33D6F4}"/>
+    <hyperlink ref="G39" r:id="rId132" xr:uid="{02756A59-0545-4A40-8CC1-01FCFDA1877A}"/>
+    <hyperlink ref="G7" r:id="rId133" display="https://ifrcorg.sharepoint.com/sites/PERcoreworkinggroup-PERcoreworkinggroup/Shared Documents/PER core working group/PER Resources/../../../../IFRCSharing/NS%20Preparedness/Forms/AllItems.aspx?id=%2Fsites%2FIFRCSharing%2FNS%20Preparedness%2FPER%20Promotional%20pack%2FPER%20Promotional%20pack%20EN%2FPER%20in%20operations&amp;p=true&amp;ga=1" xr:uid="{3515EDD3-49BB-4408-9794-335FBE22B273}"/>
+    <hyperlink ref="G8" r:id="rId134" xr:uid="{CEF90331-72A7-4DE7-A3C8-A528F2AD1CF9}"/>
+    <hyperlink ref="H26" r:id="rId135" xr:uid="{503C9430-5D46-4594-9BC5-D4D668CD5096}"/>
+    <hyperlink ref="I26" r:id="rId136" xr:uid="{5C6AAC02-3ED8-4F40-89F4-D75D43A21AC6}"/>
+    <hyperlink ref="J26" r:id="rId137" xr:uid="{86EEBAE6-81E3-424C-B7A2-35B523A3AEAB}"/>
+    <hyperlink ref="J27" r:id="rId138" xr:uid="{BC5DD859-08CC-404D-9739-AC33ECA82B21}"/>
+    <hyperlink ref="J29" r:id="rId139" xr:uid="{4DE57DA8-76F2-4502-B9B5-A81795AFABED}"/>
+    <hyperlink ref="J30" r:id="rId140" xr:uid="{F40FC23E-895D-4507-AC03-491034B0AB37}"/>
+    <hyperlink ref="J31" r:id="rId141" xr:uid="{6A47AA25-4498-4369-AD14-7557B9545C95}"/>
+    <hyperlink ref="J32" r:id="rId142" xr:uid="{0AF3B608-5E6E-4892-8AC1-62122A43C94A}"/>
+    <hyperlink ref="I27" r:id="rId143" xr:uid="{617BD3EA-5F12-4E63-AB51-EB86EC84C5D9}"/>
+    <hyperlink ref="I29" r:id="rId144" xr:uid="{E28FB437-33AA-41FB-9BDC-AFC8ADC6F98C}"/>
+    <hyperlink ref="I31" r:id="rId145" xr:uid="{226630D7-A908-46F6-AF25-5362B3E6D520}"/>
+    <hyperlink ref="H27" r:id="rId146" xr:uid="{92DCCCB2-E390-4FF5-964F-CF255172C970}"/>
+    <hyperlink ref="H32" r:id="rId147" xr:uid="{8B94F07A-B6F0-4910-B369-6324572D95D8}"/>
+    <hyperlink ref="H30" r:id="rId148" xr:uid="{C594479A-A165-4172-BEBA-3250E09602D6}"/>
+    <hyperlink ref="H31" r:id="rId149" xr:uid="{FAA58887-1A60-4BFB-AE33-02B3C5019098}"/>
+    <hyperlink ref="H29" r:id="rId150" xr:uid="{A1FF3925-2AAE-4A8A-98B8-6771A0D3D8F5}"/>
+    <hyperlink ref="J25" r:id="rId151" xr:uid="{8B1E9A0C-4E7B-40F7-8E1B-6570395774AE}"/>
+    <hyperlink ref="J33" r:id="rId152" xr:uid="{97AFCE22-3FE7-4652-A5B9-F126646A686F}"/>
+    <hyperlink ref="J34" r:id="rId153" xr:uid="{5C2CA921-9964-4884-9A7D-CFAE5481C20B}"/>
+    <hyperlink ref="J35" r:id="rId154" xr:uid="{8F84E695-F052-48A6-9479-86485D748EA6}"/>
+    <hyperlink ref="I33" r:id="rId155" xr:uid="{63B6C27C-D1E3-437E-AE0D-BF6387BEDA09}"/>
+    <hyperlink ref="I34" r:id="rId156" xr:uid="{7D32D40D-BC32-409F-818A-ED325B5200BD}"/>
+    <hyperlink ref="I35" r:id="rId157" xr:uid="{79381DF7-9C43-4116-9465-791772C115FC}"/>
+    <hyperlink ref="H33" r:id="rId158" xr:uid="{9E9D9B07-32C7-4D0B-8A69-E655146CC5D2}"/>
+    <hyperlink ref="H34" r:id="rId159" xr:uid="{3163411C-6B99-4767-8273-E9121EB6E4B0}"/>
+    <hyperlink ref="H35" r:id="rId160" xr:uid="{BE3C1DA3-DB77-41CE-BB7A-1C123ACFE81E}"/>
+    <hyperlink ref="J45" r:id="rId161" xr:uid="{A56D69F4-0FDA-4CAA-9F41-72A8EF7629E8}"/>
+    <hyperlink ref="J40" r:id="rId162" xr:uid="{FD934DC4-D36E-4D8F-A39F-99157261D90D}"/>
+    <hyperlink ref="J41" r:id="rId163" xr:uid="{182D1338-C487-4FEA-B695-FEED1B27CFEC}"/>
+    <hyperlink ref="J39" r:id="rId164" xr:uid="{4299DE75-B214-4107-AEF4-EA22090FDFB6}"/>
+    <hyperlink ref="I39" r:id="rId165" xr:uid="{5F4CE5D8-BF6B-4C8F-977E-80418AA5162F}"/>
+    <hyperlink ref="I45" r:id="rId166" xr:uid="{1E91A4B6-3CBC-45B2-9227-74BDC3AFA1C3}"/>
+    <hyperlink ref="I41" r:id="rId167" xr:uid="{CC3960BD-A2FE-4FB5-B689-D6A648E6D29A}"/>
+    <hyperlink ref="H45" r:id="rId168" xr:uid="{2EAF0381-1D0C-4DBC-AADC-4BC0946FE3C6}"/>
+    <hyperlink ref="H39" r:id="rId169" xr:uid="{9B60C769-3445-4077-AB20-97F5C49856CA}"/>
+    <hyperlink ref="H40" r:id="rId170" xr:uid="{6666B8CE-DA65-4314-82FC-99C8741B533E}"/>
+    <hyperlink ref="H41" r:id="rId171" xr:uid="{ABEDADA3-19C3-4A18-88B8-4097C1C5AA3A}"/>
+    <hyperlink ref="J36" r:id="rId172" xr:uid="{8F4147EE-B813-459B-B396-DE68A7EE0CBD}"/>
+    <hyperlink ref="I36" r:id="rId173" xr:uid="{8E2798F8-825C-456C-AE57-B660F44DDA5A}"/>
+    <hyperlink ref="H36" r:id="rId174" xr:uid="{524FF2F8-5BB0-48EA-B8CF-B686EB0AEF83}"/>
+    <hyperlink ref="G45" r:id="rId175" xr:uid="{01D02CD7-AE45-4CBE-865C-0571ABBE2098}"/>
+    <hyperlink ref="G50" r:id="rId176" xr:uid="{D14FB618-5A0A-43F3-B563-B899DAA94CDB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="133e5729-7bb1-4685-bd1f-c5e580a2ee33" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="41fc2dd8-c0a0-4082-a3dc-9303583297a2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D74ADE06E7A6647867AD30FD7257C26" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d8a53e7b88a08d9ac5326478733ecc8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="41fc2dd8-c0a0-4082-a3dc-9303583297a2" xmlns:ns3="133e5729-7bb1-4685-bd1f-c5e580a2ee33" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e14e8688653c13395930d509a3459956" ns2:_="" ns3:_="">
-    <xsd:import namespace="41fc2dd8-c0a0-4082-a3dc-9303583297a2"/>
-    <xsd:import namespace="133e5729-7bb1-4685-bd1f-c5e580a2ee33"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010012ABC7A2EA15C049AD617DE6DB5290A9" ma:contentTypeVersion="8" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="44a23c26d648525ee794dfa6e00afc15">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ceb7362a-bda1-4534-bc40-0bcb1391b5a4" xmlns:ns3="02e1a8b7-43e0-49a0-ac64-f80c71f364f4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0d4ec845133c5c2a1fc7fef1b0aa194d" ns2:_="" ns3:_="">
+    <xsd:import namespace="ceb7362a-bda1-4534-bc40-0bcb1391b5a4"/>
+    <xsd:import namespace="02e1a8b7-43e0-49a0-ac64-f80c71f364f4"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -31219,18 +31447,10 @@
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -31238,7 +31458,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="41fc2dd8-c0a0-4082-a3dc-9303583297a2" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ceb7362a-bda1-4534-bc40-0bcb1391b5a4" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -31263,60 +31483,21 @@
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="214f832c-f6f1-485d-8901-6765a4832c56" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="133e5729-7bb1-4685-bd1f-c5e580a2ee33" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="02e1a8b7-43e0-49a0-ac64-f80c71f364f4" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -31335,23 +31516,12 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{5cc3d5bd-c7ff-448c-a8db-21860a682db1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="133e5729-7bb1-4685-bd1f-c5e580a2ee33">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -31363,8 +31533,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -31453,40 +31623,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C142868B-CD2C-4A65-927F-4EA07EE49F98}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="133e5729-7bb1-4685-bd1f-c5e580a2ee33"/>
-    <ds:schemaRef ds:uri="41fc2dd8-c0a0-4082-a3dc-9303583297a2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4397ABC-053A-43A6-9751-90E336C0744C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D32D9F6E-6AC9-4398-98E9-D8FF315DEB1B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D32D9F6E-6AC9-4398-98E9-D8FF315DEB1B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E8FD31B-7F15-4BFA-8E4A-38E17E0ADAFE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="41fc2dd8-c0a0-4082-a3dc-9303583297a2"/>
-    <ds:schemaRef ds:uri="133e5729-7bb1-4685-bd1f-c5e580a2ee33"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C142868B-CD2C-4A65-927F-4EA07EE49F98}"/>
 </file>